--- a/템플릿/LH50억~100억(소방)_템플릿.xlsx
+++ b/템플릿/LH50억~100억(소방)_템플릿.xlsx
@@ -71,10 +71,6 @@
   </si>
   <si>
     <t>실적만점</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>5년2배수</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -311,6 +307,10 @@
     <t xml:space="preserve">88점이상:3점/85점이상:2점/83점이상:1.5점/80점이상:1점 </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>5년3배수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -326,7 +326,7 @@
     <numFmt numFmtId="181" formatCode="0.00_ "/>
     <numFmt numFmtId="182" formatCode="0.000%"/>
     <numFmt numFmtId="183" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="185" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="184" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -1751,6 +1751,318 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="9" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="56" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="15" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="10" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="15" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="10" fillId="0" borderId="57" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="15" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="10" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="10" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="20" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="20" fillId="10" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="10" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="10" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="9" borderId="51" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="10" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="10" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="15" fillId="0" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="10" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="10" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="20" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="10" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="20" fillId="10" borderId="48" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="20" fillId="10" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="17" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="22" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="10" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="20" fillId="10" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="10" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="20" fillId="10" borderId="47" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="20" fillId="10" borderId="44" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="10" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="20" fillId="10" borderId="47" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="20" fillId="10" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="15" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="10" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="20" fillId="10" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="10" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="10" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1842,6 +2154,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="11" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="15" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1859,9 +2174,18 @@
     <xf numFmtId="10" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="21" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1882,330 +2206,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="21" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="9" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="56" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="10" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="10" fillId="0" borderId="57" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="185" fontId="15" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="20" fillId="10" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="20" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="10" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="20" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="20" fillId="10" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="20" fillId="10" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="20" fillId="10" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="9" borderId="51" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="20" fillId="10" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="20" fillId="10" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="10" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="10" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="20" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="10" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="20" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="20" fillId="10" borderId="48" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="20" fillId="10" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="20" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="22" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="20" fillId="10" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="20" fillId="10" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="20" fillId="10" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="20" fillId="10" borderId="47" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="20" fillId="10" borderId="44" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="10" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="20" fillId="10" borderId="47" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="20" fillId="10" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="20" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="10" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="20" fillId="10" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="10" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="10" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2528,15 +2528,15 @@
       <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
+      <c r="D1" s="275"/>
+      <c r="E1" s="275"/>
       <c r="F1" s="4"/>
       <c r="G1" s="5"/>
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="177"/>
-      <c r="J1" s="178"/>
+      <c r="I1" s="276"/>
+      <c r="J1" s="277"/>
       <c r="K1" s="7" t="s">
         <v>5</v>
       </c>
@@ -2551,31 +2551,31 @@
       <c r="T1" s="9"/>
       <c r="U1" s="9"/>
       <c r="V1" s="9"/>
-      <c r="W1" s="170" t="s">
-        <v>2</v>
-      </c>
-      <c r="X1" s="170"/>
-      <c r="Y1" s="171" t="s">
+      <c r="W1" s="278" t="s">
+        <v>2</v>
+      </c>
+      <c r="X1" s="278"/>
+      <c r="Y1" s="279" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="172"/>
-      <c r="AA1" s="173" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB1" s="174"/>
+      <c r="Z1" s="280"/>
+      <c r="AA1" s="281" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB1" s="282"/>
       <c r="AC1" s="10"/>
       <c r="AD1" s="10"/>
-      <c r="AE1" s="175" t="s">
+      <c r="AE1" s="283" t="s">
         <v>7</v>
       </c>
-      <c r="AF1" s="176"/>
-      <c r="AG1" s="159">
+      <c r="AF1" s="284"/>
+      <c r="AG1" s="263">
         <f>D1</f>
         <v>0</v>
       </c>
-      <c r="AH1" s="159"/>
-      <c r="AI1" s="159"/>
-      <c r="AJ1" s="159"/>
+      <c r="AH1" s="263"/>
+      <c r="AI1" s="263"/>
+      <c r="AJ1" s="263"/>
       <c r="AK1" s="11" t="s">
         <v>8</v>
       </c>
@@ -2590,63 +2590,63 @@
       <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
+      <c r="D2" s="264"/>
+      <c r="E2" s="264"/>
       <c r="F2" s="15"/>
       <c r="G2" s="16"/>
       <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="161">
+      <c r="I2" s="265">
         <f>D2*3</f>
         <v>0</v>
       </c>
-      <c r="J2" s="162"/>
+      <c r="J2" s="266"/>
       <c r="K2" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="M2" s="267" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="179" t="s">
+      <c r="N2" s="268"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="268"/>
+      <c r="Q2" s="19" t="s">
         <v>13</v>
-      </c>
-      <c r="N2" s="163"/>
-      <c r="O2" s="163"/>
-      <c r="P2" s="163"/>
-      <c r="Q2" s="19" t="s">
-        <v>14</v>
       </c>
       <c r="R2" s="19"/>
       <c r="S2" s="19"/>
       <c r="T2" s="20"/>
       <c r="U2" s="21"/>
       <c r="V2" s="21"/>
-      <c r="W2" s="164"/>
-      <c r="X2" s="164"/>
-      <c r="Y2" s="165">
+      <c r="W2" s="269"/>
+      <c r="X2" s="269"/>
+      <c r="Y2" s="270">
         <f>I1</f>
         <v>0</v>
       </c>
-      <c r="Z2" s="166"/>
-      <c r="AA2" s="167" t="e">
+      <c r="Z2" s="271"/>
+      <c r="AA2" s="272" t="e">
         <f>TRUNC(W2/Y2,4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB2" s="168"/>
+      <c r="AB2" s="273"/>
       <c r="AC2" s="22"/>
-      <c r="AD2" s="180"/>
-      <c r="AE2" s="180"/>
-      <c r="AF2" s="180"/>
-      <c r="AG2" s="180"/>
-      <c r="AH2" s="180"/>
-      <c r="AI2" s="180"/>
-      <c r="AJ2" s="180"/>
-      <c r="AK2" s="180"/>
-      <c r="AL2" s="180"/>
-      <c r="AM2" s="181"/>
+      <c r="AD2" s="274"/>
+      <c r="AE2" s="274"/>
+      <c r="AF2" s="274"/>
+      <c r="AG2" s="274"/>
+      <c r="AH2" s="274"/>
+      <c r="AI2" s="274"/>
+      <c r="AJ2" s="274"/>
+      <c r="AK2" s="274"/>
+      <c r="AL2" s="274"/>
+      <c r="AM2" s="133"/>
       <c r="AN2" s="24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO2" s="25"/>
       <c r="AP2" s="24"/>
@@ -2654,273 +2654,273 @@
       <c r="AR2" s="24"/>
       <c r="AS2" s="1"/>
       <c r="AT2" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="AU2" s="145">
+        <v>15</v>
+      </c>
+      <c r="AU2" s="249">
         <f>AG1</f>
         <v>0</v>
       </c>
-      <c r="AV2" s="146"/>
+      <c r="AV2" s="250"/>
       <c r="AY2" s="27"/>
     </row>
     <row r="3" spans="1:52" s="28" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="147" t="s">
+      <c r="A3" s="251" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="253" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="149" t="s">
+      <c r="C3" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="151" t="s">
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="257"/>
+      <c r="I3" s="255" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="152"/>
-      <c r="E3" s="152"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="152"/>
-      <c r="H3" s="153"/>
-      <c r="I3" s="151" t="s">
+      <c r="J3" s="256"/>
+      <c r="K3" s="256"/>
+      <c r="L3" s="256"/>
+      <c r="M3" s="257"/>
+      <c r="N3" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="152"/>
-      <c r="K3" s="152"/>
-      <c r="L3" s="152"/>
-      <c r="M3" s="153"/>
-      <c r="N3" s="154" t="s">
+      <c r="O3" s="260" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="156" t="s">
+      <c r="P3" s="255" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="151" t="s">
+      <c r="Q3" s="256"/>
+      <c r="R3" s="262"/>
+      <c r="S3" s="262"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="257"/>
+      <c r="V3" s="132"/>
+      <c r="W3" s="255" t="s">
         <v>23</v>
       </c>
-      <c r="Q3" s="152"/>
-      <c r="R3" s="158"/>
-      <c r="S3" s="158"/>
-      <c r="T3" s="152"/>
-      <c r="U3" s="153"/>
-      <c r="V3" s="132"/>
-      <c r="W3" s="151" t="s">
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
+      <c r="AA3" s="256"/>
+      <c r="AB3" s="256"/>
+      <c r="AC3" s="256"/>
+      <c r="AD3" s="256"/>
+      <c r="AE3" s="257"/>
+      <c r="AF3" s="255"/>
+      <c r="AG3" s="256"/>
+      <c r="AH3" s="256"/>
+      <c r="AI3" s="256"/>
+      <c r="AJ3" s="256"/>
+      <c r="AK3" s="256"/>
+      <c r="AL3" s="256"/>
+      <c r="AM3" s="257"/>
+      <c r="AN3" s="242" t="s">
         <v>24</v>
       </c>
-      <c r="X3" s="152"/>
-      <c r="Y3" s="152"/>
-      <c r="Z3" s="152"/>
-      <c r="AA3" s="152"/>
-      <c r="AB3" s="152"/>
-      <c r="AC3" s="152"/>
-      <c r="AD3" s="152"/>
-      <c r="AE3" s="153"/>
-      <c r="AF3" s="151"/>
-      <c r="AG3" s="152"/>
-      <c r="AH3" s="152"/>
-      <c r="AI3" s="152"/>
-      <c r="AJ3" s="152"/>
-      <c r="AK3" s="152"/>
-      <c r="AL3" s="152"/>
-      <c r="AM3" s="153"/>
-      <c r="AN3" s="138" t="s">
+      <c r="AO3" s="238" t="s">
         <v>25</v>
       </c>
-      <c r="AO3" s="134" t="s">
+      <c r="AP3" s="244" t="s">
         <v>26</v>
       </c>
-      <c r="AP3" s="140" t="s">
+      <c r="AQ3" s="246" t="s">
         <v>27</v>
       </c>
-      <c r="AQ3" s="142" t="s">
+      <c r="AR3" s="248" t="s">
         <v>28</v>
       </c>
-      <c r="AR3" s="144" t="s">
+      <c r="AS3" s="237" t="s">
         <v>29</v>
       </c>
-      <c r="AS3" s="133" t="s">
+      <c r="AT3" s="238" t="s">
         <v>30</v>
       </c>
-      <c r="AT3" s="134" t="s">
+      <c r="AU3" s="237" t="s">
         <v>31</v>
       </c>
-      <c r="AU3" s="133" t="s">
+      <c r="AV3" s="237" t="s">
         <v>32</v>
       </c>
-      <c r="AV3" s="133" t="s">
+      <c r="AW3" s="237" t="s">
         <v>33</v>
       </c>
-      <c r="AW3" s="133" t="s">
+      <c r="AX3" s="240" t="s">
         <v>34</v>
       </c>
-      <c r="AX3" s="136" t="s">
+      <c r="AY3" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="AY3" s="133" t="s">
+      <c r="AZ3" s="237" t="s">
         <v>36</v>
-      </c>
-      <c r="AZ3" s="133" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:52" s="28" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="148"/>
-      <c r="B4" s="150"/>
+      <c r="A4" s="252"/>
+      <c r="B4" s="254"/>
       <c r="C4" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="E4" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="F4" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="132" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="M4" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="132" t="s">
+      <c r="N4" s="259"/>
+      <c r="O4" s="261"/>
+      <c r="P4" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="Q4" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="U4" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="V4" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="W4" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="X4" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="Y4" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" s="30" t="s">
+      <c r="Z4" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="M4" s="35" t="s">
+      <c r="AA4" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N4" s="155"/>
-      <c r="O4" s="157"/>
-      <c r="P4" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="R4" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="S4" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="T4" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="U4" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="V4" s="37" t="s">
+      <c r="AB4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="W4" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="X4" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y4" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z4" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA4" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB4" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="40" t="s">
+      <c r="AD4" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="AD4" s="41" t="s">
+      <c r="AE4" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="AE4" s="41" t="s">
+      <c r="AF4" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="AF4" s="42" t="s">
+      <c r="AG4" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="AG4" s="42" t="s">
+      <c r="AH4" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="AH4" s="43" t="s">
+      <c r="AI4" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="AI4" s="43" t="s">
+      <c r="AJ4" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="AJ4" s="43" t="s">
+      <c r="AK4" s="44" t="s">
         <v>61</v>
-      </c>
-      <c r="AK4" s="44" t="s">
-        <v>62</v>
       </c>
       <c r="AL4" s="44"/>
       <c r="AM4" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN4" s="139"/>
-      <c r="AO4" s="135"/>
-      <c r="AP4" s="141"/>
-      <c r="AQ4" s="143"/>
-      <c r="AR4" s="144"/>
-      <c r="AS4" s="133"/>
-      <c r="AT4" s="135"/>
-      <c r="AU4" s="133"/>
-      <c r="AV4" s="133"/>
-      <c r="AW4" s="133"/>
-      <c r="AX4" s="137"/>
-      <c r="AY4" s="133"/>
-      <c r="AZ4" s="133"/>
+        <v>62</v>
+      </c>
+      <c r="AN4" s="243"/>
+      <c r="AO4" s="239"/>
+      <c r="AP4" s="245"/>
+      <c r="AQ4" s="247"/>
+      <c r="AR4" s="248"/>
+      <c r="AS4" s="237"/>
+      <c r="AT4" s="239"/>
+      <c r="AU4" s="237"/>
+      <c r="AV4" s="237"/>
+      <c r="AW4" s="237"/>
+      <c r="AX4" s="241"/>
+      <c r="AY4" s="237"/>
+      <c r="AZ4" s="237"/>
     </row>
     <row r="5" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="45"/>
       <c r="B5" s="87"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="183"/>
-      <c r="E5" s="184"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="186"/>
-      <c r="H5" s="187"/>
-      <c r="I5" s="188"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="135"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="138"/>
+      <c r="H5" s="139"/>
+      <c r="I5" s="140"/>
       <c r="J5" s="123"/>
       <c r="K5" s="123"/>
-      <c r="L5" s="189"/>
-      <c r="M5" s="190"/>
-      <c r="N5" s="191">
+      <c r="L5" s="141"/>
+      <c r="M5" s="142"/>
+      <c r="N5" s="143">
         <f t="shared" ref="N5:N43" si="0">SUM(I5:M5)</f>
         <v>0</v>
       </c>
-      <c r="O5" s="192">
-        <v>1</v>
-      </c>
-      <c r="P5" s="193"/>
-      <c r="Q5" s="194"/>
-      <c r="R5" s="195"/>
-      <c r="S5" s="196"/>
-      <c r="T5" s="197"/>
-      <c r="U5" s="198">
+      <c r="O5" s="144">
+        <v>1</v>
+      </c>
+      <c r="P5" s="145"/>
+      <c r="Q5" s="146"/>
+      <c r="R5" s="147"/>
+      <c r="S5" s="148"/>
+      <c r="T5" s="149"/>
+      <c r="U5" s="150">
         <f>ROUND(((P5*I5)+(Q5*J5)+(R5*K5)+(S5*L5)+(T5*M5))*O5,2)</f>
         <v>0</v>
       </c>
-      <c r="V5" s="199">
+      <c r="V5" s="151">
         <f>IF(U5&gt;=15,15,U5)</f>
         <v>0</v>
       </c>
-      <c r="W5" s="200"/>
-      <c r="X5" s="201"/>
-      <c r="Y5" s="201"/>
-      <c r="Z5" s="202"/>
-      <c r="AA5" s="203"/>
-      <c r="AB5" s="204" t="e">
+      <c r="W5" s="152"/>
+      <c r="X5" s="153"/>
+      <c r="Y5" s="153"/>
+      <c r="Z5" s="154"/>
+      <c r="AA5" s="155"/>
+      <c r="AB5" s="156" t="e">
         <f>ROUND((((W5*I5)+(X5*J5)+(Y5*K5)+(Z5*L5)+(AA5*M5))/$I$2),2)*13</f>
         <v>#DIV/0!</v>
       </c>
@@ -2990,13 +2990,13 @@
     <row r="6" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="45"/>
       <c r="B6" s="46"/>
-      <c r="C6" s="205" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="206"/>
-      <c r="G6" s="207"/>
+      <c r="C6" s="232" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="233"/>
+      <c r="E6" s="233"/>
+      <c r="F6" s="233"/>
+      <c r="G6" s="234"/>
       <c r="H6" s="122"/>
       <c r="I6" s="89"/>
       <c r="J6" s="130"/>
@@ -3024,7 +3024,7 @@
       <c r="AC6" s="59"/>
       <c r="AD6" s="56"/>
       <c r="AE6" s="56"/>
-      <c r="AF6" s="208"/>
+      <c r="AF6" s="157"/>
       <c r="AG6" s="100"/>
       <c r="AH6" s="63"/>
       <c r="AI6" s="101"/>
@@ -3051,16 +3051,16 @@
     <row r="7" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45"/>
       <c r="B7" s="87"/>
-      <c r="C7" s="184"/>
-      <c r="D7" s="209"/>
-      <c r="E7" s="210"/>
-      <c r="F7" s="210"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="158"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
       <c r="G7" s="103"/>
-      <c r="H7" s="211"/>
+      <c r="H7" s="160"/>
       <c r="I7" s="48"/>
       <c r="J7" s="50"/>
       <c r="K7" s="124"/>
-      <c r="L7" s="212"/>
+      <c r="L7" s="161"/>
       <c r="M7" s="104"/>
       <c r="N7" s="52">
         <f t="shared" si="0"/>
@@ -3072,7 +3072,7 @@
       <c r="P7" s="54"/>
       <c r="Q7" s="55"/>
       <c r="R7" s="125"/>
-      <c r="S7" s="213"/>
+      <c r="S7" s="162"/>
       <c r="T7" s="95"/>
       <c r="U7" s="56">
         <f>ROUND(((P7*I7)+(Q7*J7)+(R7*K7)+(S7*L7)+(T7*M7))*O7,2)</f>
@@ -3082,10 +3082,10 @@
         <f t="shared" ref="V7:V79" si="2">IF(U7&gt;=15,15,U7)</f>
         <v>0</v>
       </c>
-      <c r="W7" s="214"/>
-      <c r="X7" s="214"/>
+      <c r="W7" s="163"/>
+      <c r="X7" s="163"/>
       <c r="Y7" s="131"/>
-      <c r="Z7" s="215"/>
+      <c r="Z7" s="164"/>
       <c r="AA7" s="99"/>
       <c r="AB7" s="58" t="e">
         <f t="shared" ref="AB7:AB79" si="3">ROUND((((W7*I7)+(X7*J7)+(Y7*K7)+(Z7*L7)+(AA7*M7))/$I$2),2)*13</f>
@@ -3102,7 +3102,7 @@
         <f t="shared" ref="AE7:AE79" si="5">IF((AC7+AD7)&gt;=15,15,(AC7+AD7))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF7" s="216"/>
+      <c r="AF7" s="165"/>
       <c r="AG7" s="62"/>
       <c r="AH7" s="63" t="e">
         <f t="shared" ref="AH7:AH79" si="6">IF((V7+AE7+AF7)&gt;=30,30,(V7+AE7+AF7))</f>
@@ -3134,8 +3134,8 @@
         <f t="shared" ref="AP7:AQ61" si="10">100%+AO7</f>
         <v>1</v>
       </c>
-      <c r="AQ7" s="217"/>
-      <c r="AR7" s="218"/>
+      <c r="AQ7" s="166"/>
+      <c r="AR7" s="167"/>
       <c r="AS7" s="71"/>
       <c r="AT7" s="72"/>
       <c r="AU7" s="72"/>
@@ -3154,13 +3154,13 @@
     <row r="8" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="45"/>
       <c r="B8" s="46"/>
-      <c r="C8" s="205" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="206"/>
-      <c r="E8" s="206"/>
-      <c r="F8" s="206"/>
-      <c r="G8" s="207"/>
+      <c r="C8" s="232" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="233"/>
+      <c r="E8" s="233"/>
+      <c r="F8" s="233"/>
+      <c r="G8" s="234"/>
       <c r="H8" s="122"/>
       <c r="I8" s="89"/>
       <c r="J8" s="130"/>
@@ -3188,7 +3188,7 @@
       <c r="AC8" s="59"/>
       <c r="AD8" s="56"/>
       <c r="AE8" s="56"/>
-      <c r="AF8" s="208"/>
+      <c r="AF8" s="157"/>
       <c r="AG8" s="100"/>
       <c r="AH8" s="63"/>
       <c r="AI8" s="101"/>
@@ -3215,29 +3215,29 @@
     <row r="9" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="45"/>
       <c r="B9" s="87"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="219"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="220"/>
-      <c r="G9" s="221"/>
-      <c r="H9" s="221"/>
-      <c r="I9" s="222"/>
-      <c r="J9" s="223"/>
-      <c r="K9" s="224"/>
-      <c r="L9" s="225"/>
-      <c r="M9" s="226"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="168"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="169"/>
+      <c r="G9" s="170"/>
+      <c r="H9" s="170"/>
+      <c r="I9" s="171"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="173"/>
+      <c r="L9" s="174"/>
+      <c r="M9" s="175"/>
       <c r="N9" s="78">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O9" s="227">
-        <v>1</v>
-      </c>
-      <c r="P9" s="228"/>
-      <c r="Q9" s="229"/>
-      <c r="R9" s="230"/>
-      <c r="S9" s="231"/>
-      <c r="T9" s="232"/>
+      <c r="O9" s="176">
+        <v>1</v>
+      </c>
+      <c r="P9" s="177"/>
+      <c r="Q9" s="178"/>
+      <c r="R9" s="179"/>
+      <c r="S9" s="180"/>
+      <c r="T9" s="181"/>
       <c r="U9" s="79">
         <f t="shared" ref="U9:U79" si="12">ROUND(((P9*I9)+(Q9*J9)+(R9*K9)+(S9*L9)+(T9*M9))*O9,2)</f>
         <v>0</v>
@@ -3246,11 +3246,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W9" s="233"/>
-      <c r="X9" s="234"/>
-      <c r="Y9" s="233"/>
-      <c r="Z9" s="235"/>
-      <c r="AA9" s="236"/>
+      <c r="W9" s="182"/>
+      <c r="X9" s="183"/>
+      <c r="Y9" s="182"/>
+      <c r="Z9" s="184"/>
+      <c r="AA9" s="185"/>
       <c r="AB9" s="81" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
@@ -3266,7 +3266,7 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF9" s="216"/>
+      <c r="AF9" s="165"/>
       <c r="AG9" s="62"/>
       <c r="AH9" s="66" t="e">
         <f t="shared" si="6"/>
@@ -3294,20 +3294,20 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO9" s="84"/>
-      <c r="AP9" s="237">
-        <v>2</v>
-      </c>
-      <c r="AQ9" s="238">
+      <c r="AP9" s="186">
+        <v>2</v>
+      </c>
+      <c r="AQ9" s="187">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="AR9" s="218"/>
+      <c r="AR9" s="167"/>
       <c r="AS9" s="71"/>
       <c r="AT9" s="85"/>
-      <c r="AU9" s="239"/>
+      <c r="AU9" s="188"/>
       <c r="AV9" s="85"/>
-      <c r="AW9" s="240"/>
-      <c r="AX9" s="241"/>
+      <c r="AW9" s="189"/>
+      <c r="AX9" s="190"/>
       <c r="AY9" s="86">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -3320,13 +3320,13 @@
     <row r="10" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45"/>
       <c r="B10" s="46"/>
-      <c r="C10" s="205" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="206"/>
-      <c r="E10" s="206"/>
-      <c r="F10" s="206"/>
-      <c r="G10" s="207"/>
+      <c r="C10" s="232" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="233"/>
+      <c r="G10" s="234"/>
       <c r="H10" s="122"/>
       <c r="I10" s="89"/>
       <c r="J10" s="130"/>
@@ -3354,7 +3354,7 @@
       <c r="AC10" s="59"/>
       <c r="AD10" s="56"/>
       <c r="AE10" s="56"/>
-      <c r="AF10" s="208"/>
+      <c r="AF10" s="157"/>
       <c r="AG10" s="100"/>
       <c r="AH10" s="63"/>
       <c r="AI10" s="101"/>
@@ -3381,13 +3381,13 @@
     <row r="11" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="45"/>
       <c r="B11" s="87"/>
-      <c r="C11" s="219"/>
-      <c r="D11" s="210"/>
-      <c r="E11" s="210"/>
-      <c r="F11" s="209"/>
+      <c r="C11" s="168"/>
+      <c r="D11" s="159"/>
+      <c r="E11" s="159"/>
+      <c r="F11" s="158"/>
       <c r="G11" s="103"/>
-      <c r="H11" s="211"/>
-      <c r="I11" s="242"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="191"/>
       <c r="J11" s="124"/>
       <c r="K11" s="124"/>
       <c r="L11" s="50"/>
@@ -3396,13 +3396,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O11" s="227">
-        <v>1</v>
-      </c>
-      <c r="P11" s="243"/>
-      <c r="Q11" s="244"/>
-      <c r="R11" s="244"/>
-      <c r="S11" s="245"/>
+      <c r="O11" s="176">
+        <v>1</v>
+      </c>
+      <c r="P11" s="192"/>
+      <c r="Q11" s="193"/>
+      <c r="R11" s="193"/>
+      <c r="S11" s="194"/>
       <c r="T11" s="95"/>
       <c r="U11" s="56">
         <f t="shared" si="12"/>
@@ -3464,10 +3464,10 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AQ11" s="217">
-        <v>1</v>
-      </c>
-      <c r="AR11" s="218"/>
+      <c r="AQ11" s="166">
+        <v>1</v>
+      </c>
+      <c r="AR11" s="167"/>
       <c r="AS11" s="128"/>
       <c r="AT11" s="72"/>
       <c r="AU11" s="131"/>
@@ -3486,13 +3486,13 @@
     <row r="12" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45"/>
       <c r="B12" s="46"/>
-      <c r="C12" s="205" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="206"/>
-      <c r="E12" s="206"/>
-      <c r="F12" s="206"/>
-      <c r="G12" s="207"/>
+      <c r="C12" s="232" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="233"/>
+      <c r="E12" s="233"/>
+      <c r="F12" s="233"/>
+      <c r="G12" s="234"/>
       <c r="H12" s="122"/>
       <c r="I12" s="130"/>
       <c r="J12" s="130"/>
@@ -3520,7 +3520,7 @@
       <c r="AC12" s="59"/>
       <c r="AD12" s="56"/>
       <c r="AE12" s="56"/>
-      <c r="AF12" s="208"/>
+      <c r="AF12" s="157"/>
       <c r="AG12" s="100"/>
       <c r="AH12" s="63"/>
       <c r="AI12" s="101"/>
@@ -3547,13 +3547,13 @@
     <row r="13" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45"/>
       <c r="B13" s="87"/>
-      <c r="C13" s="210"/>
-      <c r="D13" s="219"/>
-      <c r="E13" s="182"/>
-      <c r="F13" s="182"/>
+      <c r="C13" s="159"/>
+      <c r="D13" s="168"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="134"/>
       <c r="G13" s="103"/>
-      <c r="H13" s="211"/>
-      <c r="I13" s="246"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="195"/>
       <c r="J13" s="124"/>
       <c r="K13" s="124"/>
       <c r="L13" s="49"/>
@@ -3565,10 +3565,10 @@
       <c r="O13" s="53">
         <v>1</v>
       </c>
-      <c r="P13" s="244"/>
-      <c r="Q13" s="244"/>
-      <c r="R13" s="244"/>
-      <c r="S13" s="245"/>
+      <c r="P13" s="193"/>
+      <c r="Q13" s="193"/>
+      <c r="R13" s="193"/>
+      <c r="S13" s="194"/>
       <c r="T13" s="95"/>
       <c r="U13" s="56">
         <f t="shared" si="12"/>
@@ -3580,9 +3580,9 @@
       </c>
       <c r="W13" s="131"/>
       <c r="X13" s="131"/>
-      <c r="Y13" s="215"/>
+      <c r="Y13" s="164"/>
       <c r="Z13" s="77"/>
-      <c r="AA13" s="247"/>
+      <c r="AA13" s="196"/>
       <c r="AB13" s="56" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
@@ -3625,9 +3625,9 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO13" s="248"/>
-      <c r="AP13" s="217"/>
-      <c r="AQ13" s="217">
+      <c r="AO13" s="197"/>
+      <c r="AP13" s="166"/>
+      <c r="AQ13" s="166">
         <v>2</v>
       </c>
       <c r="AR13" s="70"/>
@@ -3649,13 +3649,13 @@
     <row r="14" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="45"/>
       <c r="B14" s="46"/>
-      <c r="C14" s="205" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
-      <c r="F14" s="206"/>
-      <c r="G14" s="207"/>
+      <c r="C14" s="232" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="233"/>
+      <c r="E14" s="233"/>
+      <c r="F14" s="233"/>
+      <c r="G14" s="234"/>
       <c r="H14" s="122"/>
       <c r="I14" s="89"/>
       <c r="J14" s="130"/>
@@ -3683,7 +3683,7 @@
       <c r="AC14" s="59"/>
       <c r="AD14" s="56"/>
       <c r="AE14" s="56"/>
-      <c r="AF14" s="208"/>
+      <c r="AF14" s="157"/>
       <c r="AG14" s="100"/>
       <c r="AH14" s="63"/>
       <c r="AI14" s="101"/>
@@ -3710,13 +3710,13 @@
     <row r="15" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="45"/>
       <c r="B15" s="87"/>
-      <c r="C15" s="219"/>
+      <c r="C15" s="168"/>
       <c r="D15" s="115"/>
       <c r="E15" s="115"/>
-      <c r="F15" s="249"/>
-      <c r="G15" s="221"/>
-      <c r="H15" s="211"/>
-      <c r="I15" s="246"/>
+      <c r="F15" s="198"/>
+      <c r="G15" s="170"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="195"/>
       <c r="J15" s="50"/>
       <c r="K15" s="50"/>
       <c r="L15" s="49"/>
@@ -3728,10 +3728,10 @@
       <c r="O15" s="53">
         <v>1</v>
       </c>
-      <c r="P15" s="243"/>
+      <c r="P15" s="192"/>
       <c r="Q15" s="108"/>
       <c r="R15" s="108"/>
-      <c r="S15" s="245"/>
+      <c r="S15" s="194"/>
       <c r="T15" s="95"/>
       <c r="U15" s="56">
         <f t="shared" si="12"/>
@@ -3742,9 +3742,9 @@
         <v>0</v>
       </c>
       <c r="W15" s="131"/>
-      <c r="X15" s="250"/>
+      <c r="X15" s="199"/>
       <c r="Y15" s="88"/>
-      <c r="Z15" s="250"/>
+      <c r="Z15" s="199"/>
       <c r="AA15" s="99"/>
       <c r="AB15" s="58" t="e">
         <f t="shared" si="3"/>
@@ -3788,7 +3788,7 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO15" s="248"/>
+      <c r="AO15" s="197"/>
       <c r="AP15" s="69">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -3797,7 +3797,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="AR15" s="218"/>
+      <c r="AR15" s="167"/>
       <c r="AS15" s="71"/>
       <c r="AT15" s="72"/>
       <c r="AU15" s="72"/>
@@ -3816,13 +3816,13 @@
     <row r="16" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="45"/>
       <c r="B16" s="46"/>
-      <c r="C16" s="205" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="206"/>
-      <c r="E16" s="206"/>
-      <c r="F16" s="206"/>
-      <c r="G16" s="251"/>
+      <c r="C16" s="232" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="233"/>
+      <c r="E16" s="233"/>
+      <c r="F16" s="233"/>
+      <c r="G16" s="235"/>
       <c r="H16" s="122"/>
       <c r="I16" s="89"/>
       <c r="J16" s="89"/>
@@ -3850,7 +3850,7 @@
       <c r="AC16" s="59"/>
       <c r="AD16" s="56"/>
       <c r="AE16" s="56"/>
-      <c r="AF16" s="208"/>
+      <c r="AF16" s="157"/>
       <c r="AG16" s="100"/>
       <c r="AH16" s="63"/>
       <c r="AI16" s="101"/>
@@ -3877,13 +3877,13 @@
     <row r="17" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="45"/>
       <c r="B17" s="87"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="252"/>
-      <c r="E17" s="249"/>
-      <c r="F17" s="209"/>
+      <c r="C17" s="134"/>
+      <c r="D17" s="200"/>
+      <c r="E17" s="198"/>
+      <c r="F17" s="158"/>
       <c r="G17" s="103"/>
-      <c r="H17" s="211"/>
-      <c r="I17" s="246"/>
+      <c r="H17" s="160"/>
+      <c r="I17" s="195"/>
       <c r="J17" s="124"/>
       <c r="K17" s="50"/>
       <c r="L17" s="49"/>
@@ -3956,7 +3956,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO17" s="68"/>
-      <c r="AP17" s="217">
+      <c r="AP17" s="166">
         <v>1</v>
       </c>
       <c r="AQ17" s="69">
@@ -3982,13 +3982,13 @@
     <row r="18" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="45"/>
       <c r="B18" s="46"/>
-      <c r="C18" s="205" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="206"/>
-      <c r="E18" s="206"/>
-      <c r="F18" s="206"/>
-      <c r="G18" s="251"/>
+      <c r="C18" s="232" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="233"/>
+      <c r="E18" s="233"/>
+      <c r="F18" s="233"/>
+      <c r="G18" s="235"/>
       <c r="H18" s="122"/>
       <c r="I18" s="89"/>
       <c r="J18" s="89"/>
@@ -4016,7 +4016,7 @@
       <c r="AC18" s="59"/>
       <c r="AD18" s="56"/>
       <c r="AE18" s="56"/>
-      <c r="AF18" s="208"/>
+      <c r="AF18" s="157"/>
       <c r="AG18" s="100"/>
       <c r="AH18" s="63"/>
       <c r="AI18" s="101"/>
@@ -4043,12 +4043,12 @@
     <row r="19" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="45"/>
       <c r="B19" s="87"/>
-      <c r="C19" s="182"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="209"/>
+      <c r="C19" s="134"/>
+      <c r="D19" s="168"/>
+      <c r="E19" s="158"/>
       <c r="F19" s="115"/>
       <c r="G19" s="103"/>
-      <c r="H19" s="211"/>
+      <c r="H19" s="160"/>
       <c r="I19" s="48"/>
       <c r="J19" s="124"/>
       <c r="K19" s="124"/>
@@ -4062,8 +4062,8 @@
         <v>1</v>
       </c>
       <c r="P19" s="54"/>
-      <c r="Q19" s="244"/>
-      <c r="R19" s="244"/>
+      <c r="Q19" s="193"/>
+      <c r="R19" s="193"/>
       <c r="S19" s="76"/>
       <c r="T19" s="95"/>
       <c r="U19" s="56">
@@ -4074,10 +4074,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W19" s="250"/>
+      <c r="W19" s="199"/>
       <c r="X19" s="131"/>
       <c r="Y19" s="126"/>
-      <c r="Z19" s="250"/>
+      <c r="Z19" s="199"/>
       <c r="AA19" s="99"/>
       <c r="AB19" s="58" t="e">
         <f t="shared" si="3"/>
@@ -4122,10 +4122,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO19" s="68"/>
-      <c r="AP19" s="217">
-        <v>1</v>
-      </c>
-      <c r="AQ19" s="217">
+      <c r="AP19" s="166">
+        <v>1</v>
+      </c>
+      <c r="AQ19" s="166">
         <v>3</v>
       </c>
       <c r="AR19" s="70"/>
@@ -4147,13 +4147,13 @@
     <row r="20" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="45"/>
       <c r="B20" s="46"/>
-      <c r="C20" s="205" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="206"/>
-      <c r="E20" s="206"/>
-      <c r="F20" s="206"/>
-      <c r="G20" s="251"/>
+      <c r="C20" s="232" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="233"/>
+      <c r="E20" s="233"/>
+      <c r="F20" s="233"/>
+      <c r="G20" s="235"/>
       <c r="H20" s="122"/>
       <c r="I20" s="89"/>
       <c r="J20" s="89"/>
@@ -4181,7 +4181,7 @@
       <c r="AC20" s="59"/>
       <c r="AD20" s="56"/>
       <c r="AE20" s="56"/>
-      <c r="AF20" s="208"/>
+      <c r="AF20" s="157"/>
       <c r="AG20" s="100"/>
       <c r="AH20" s="63"/>
       <c r="AI20" s="101"/>
@@ -4208,13 +4208,13 @@
     <row r="21" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="45"/>
       <c r="B21" s="87"/>
-      <c r="C21" s="219"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="210"/>
+      <c r="C21" s="168"/>
+      <c r="D21" s="200"/>
+      <c r="E21" s="159"/>
       <c r="F21" s="115"/>
-      <c r="G21" s="253"/>
-      <c r="H21" s="211"/>
-      <c r="I21" s="246"/>
+      <c r="G21" s="201"/>
+      <c r="H21" s="160"/>
+      <c r="I21" s="195"/>
       <c r="J21" s="124"/>
       <c r="K21" s="124"/>
       <c r="L21" s="50"/>
@@ -4226,7 +4226,7 @@
       <c r="O21" s="53">
         <v>1</v>
       </c>
-      <c r="P21" s="254"/>
+      <c r="P21" s="202"/>
       <c r="Q21" s="125"/>
       <c r="R21" s="125"/>
       <c r="S21" s="76"/>
@@ -4239,7 +4239,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W21" s="234"/>
+      <c r="W21" s="183"/>
       <c r="X21" s="131"/>
       <c r="Y21" s="126"/>
       <c r="Z21" s="57"/>
@@ -4287,13 +4287,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO21" s="68"/>
-      <c r="AP21" s="217">
-        <v>2</v>
-      </c>
-      <c r="AQ21" s="217">
-        <v>2</v>
-      </c>
-      <c r="AR21" s="218"/>
+      <c r="AP21" s="166">
+        <v>2</v>
+      </c>
+      <c r="AQ21" s="166">
+        <v>2</v>
+      </c>
+      <c r="AR21" s="167"/>
       <c r="AS21" s="128"/>
       <c r="AT21" s="72"/>
       <c r="AU21" s="131"/>
@@ -4312,13 +4312,13 @@
     <row r="22" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="45"/>
       <c r="B22" s="46"/>
-      <c r="C22" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="206"/>
-      <c r="E22" s="206"/>
-      <c r="F22" s="206"/>
-      <c r="G22" s="255"/>
+      <c r="C22" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="233"/>
+      <c r="E22" s="233"/>
+      <c r="F22" s="233"/>
+      <c r="G22" s="236"/>
       <c r="H22" s="122"/>
       <c r="I22" s="130"/>
       <c r="J22" s="130"/>
@@ -4346,7 +4346,7 @@
       <c r="AC22" s="59"/>
       <c r="AD22" s="56"/>
       <c r="AE22" s="56"/>
-      <c r="AF22" s="208"/>
+      <c r="AF22" s="157"/>
       <c r="AG22" s="100"/>
       <c r="AH22" s="63"/>
       <c r="AI22" s="101"/>
@@ -4373,14 +4373,14 @@
     <row r="23" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="45"/>
       <c r="B23" s="87"/>
-      <c r="C23" s="209"/>
-      <c r="D23" s="219"/>
-      <c r="E23" s="210"/>
-      <c r="F23" s="249"/>
-      <c r="G23" s="253"/>
-      <c r="H23" s="211"/>
+      <c r="C23" s="158"/>
+      <c r="D23" s="168"/>
+      <c r="E23" s="159"/>
+      <c r="F23" s="198"/>
+      <c r="G23" s="201"/>
+      <c r="H23" s="160"/>
       <c r="I23" s="48"/>
-      <c r="J23" s="256"/>
+      <c r="J23" s="203"/>
       <c r="K23" s="124"/>
       <c r="L23" s="49"/>
       <c r="M23" s="104"/>
@@ -4394,7 +4394,7 @@
       <c r="P23" s="54"/>
       <c r="Q23" s="125"/>
       <c r="R23" s="125"/>
-      <c r="S23" s="245"/>
+      <c r="S23" s="194"/>
       <c r="T23" s="95"/>
       <c r="U23" s="56">
         <f t="shared" si="12"/>
@@ -4404,8 +4404,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W23" s="250"/>
-      <c r="X23" s="257"/>
+      <c r="W23" s="199"/>
+      <c r="X23" s="204"/>
       <c r="Y23" s="126"/>
       <c r="Z23" s="97"/>
       <c r="AA23" s="99"/>
@@ -4452,10 +4452,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO23" s="68"/>
-      <c r="AP23" s="217">
-        <v>1</v>
-      </c>
-      <c r="AQ23" s="217">
+      <c r="AP23" s="166">
+        <v>1</v>
+      </c>
+      <c r="AQ23" s="166">
         <v>1</v>
       </c>
       <c r="AR23" s="70"/>
@@ -4477,13 +4477,13 @@
     <row r="24" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A24" s="45"/>
       <c r="B24" s="46"/>
-      <c r="C24" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="206"/>
-      <c r="E24" s="206"/>
-      <c r="F24" s="206"/>
-      <c r="G24" s="207"/>
+      <c r="C24" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="233"/>
+      <c r="E24" s="233"/>
+      <c r="F24" s="233"/>
+      <c r="G24" s="234"/>
       <c r="H24" s="122"/>
       <c r="I24" s="130"/>
       <c r="J24" s="89"/>
@@ -4511,7 +4511,7 @@
       <c r="AC24" s="59"/>
       <c r="AD24" s="56"/>
       <c r="AE24" s="56"/>
-      <c r="AF24" s="208"/>
+      <c r="AF24" s="157"/>
       <c r="AG24" s="100"/>
       <c r="AH24" s="63"/>
       <c r="AI24" s="101"/>
@@ -4538,13 +4538,13 @@
     <row r="25" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="45"/>
       <c r="B25" s="87"/>
-      <c r="C25" s="219"/>
-      <c r="D25" s="219"/>
-      <c r="E25" s="210"/>
-      <c r="F25" s="249"/>
-      <c r="G25" s="253"/>
-      <c r="H25" s="211"/>
-      <c r="I25" s="246"/>
+      <c r="C25" s="168"/>
+      <c r="D25" s="168"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="198"/>
+      <c r="G25" s="201"/>
+      <c r="H25" s="160"/>
+      <c r="I25" s="195"/>
       <c r="J25" s="129"/>
       <c r="K25" s="124"/>
       <c r="L25" s="49"/>
@@ -4556,9 +4556,9 @@
       <c r="O25" s="53">
         <v>1</v>
       </c>
-      <c r="P25" s="254"/>
-      <c r="Q25" s="213"/>
-      <c r="R25" s="213"/>
+      <c r="P25" s="202"/>
+      <c r="Q25" s="162"/>
+      <c r="R25" s="162"/>
       <c r="S25" s="76"/>
       <c r="T25" s="95"/>
       <c r="U25" s="56">
@@ -4572,7 +4572,7 @@
       <c r="W25" s="131"/>
       <c r="X25" s="131"/>
       <c r="Y25" s="131"/>
-      <c r="Z25" s="247"/>
+      <c r="Z25" s="196"/>
       <c r="AA25" s="97"/>
       <c r="AB25" s="56" t="e">
         <f t="shared" si="3"/>
@@ -4617,13 +4617,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO25" s="68"/>
-      <c r="AP25" s="217">
-        <v>2</v>
-      </c>
-      <c r="AQ25" s="217">
-        <v>1</v>
-      </c>
-      <c r="AR25" s="218"/>
+      <c r="AP25" s="166">
+        <v>2</v>
+      </c>
+      <c r="AQ25" s="166">
+        <v>1</v>
+      </c>
+      <c r="AR25" s="167"/>
       <c r="AS25" s="71"/>
       <c r="AT25" s="72"/>
       <c r="AU25" s="131"/>
@@ -4642,13 +4642,13 @@
     <row r="26" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="45"/>
       <c r="B26" s="46"/>
-      <c r="C26" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="206"/>
-      <c r="E26" s="206"/>
-      <c r="F26" s="206"/>
-      <c r="G26" s="207"/>
+      <c r="C26" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="233"/>
+      <c r="E26" s="233"/>
+      <c r="F26" s="233"/>
+      <c r="G26" s="234"/>
       <c r="H26" s="122"/>
       <c r="I26" s="89"/>
       <c r="J26" s="89"/>
@@ -4676,7 +4676,7 @@
       <c r="AC26" s="59"/>
       <c r="AD26" s="56"/>
       <c r="AE26" s="56"/>
-      <c r="AF26" s="208"/>
+      <c r="AF26" s="157"/>
       <c r="AG26" s="100"/>
       <c r="AH26" s="63"/>
       <c r="AI26" s="101"/>
@@ -4703,13 +4703,13 @@
     <row r="27" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="45"/>
       <c r="B27" s="87"/>
-      <c r="C27" s="258"/>
-      <c r="D27" s="219"/>
-      <c r="E27" s="210"/>
-      <c r="F27" s="249"/>
+      <c r="C27" s="205"/>
+      <c r="D27" s="168"/>
+      <c r="E27" s="159"/>
+      <c r="F27" s="198"/>
       <c r="G27" s="103"/>
-      <c r="H27" s="211"/>
-      <c r="I27" s="246"/>
+      <c r="H27" s="160"/>
+      <c r="I27" s="195"/>
       <c r="J27" s="129"/>
       <c r="K27" s="124"/>
       <c r="L27" s="49"/>
@@ -4721,9 +4721,9 @@
       <c r="O27" s="53">
         <v>1</v>
       </c>
-      <c r="P27" s="254"/>
+      <c r="P27" s="202"/>
       <c r="Q27" s="125"/>
-      <c r="R27" s="259"/>
+      <c r="R27" s="206"/>
       <c r="S27" s="76"/>
       <c r="T27" s="95"/>
       <c r="U27" s="56">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="W27" s="131"/>
       <c r="X27" s="131"/>
-      <c r="Y27" s="234"/>
+      <c r="Y27" s="183"/>
       <c r="Z27" s="97"/>
       <c r="AA27" s="99"/>
       <c r="AB27" s="58" t="e">
@@ -4782,13 +4782,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO27" s="68"/>
-      <c r="AP27" s="217">
-        <v>1</v>
-      </c>
-      <c r="AQ27" s="217">
-        <v>1</v>
-      </c>
-      <c r="AR27" s="218"/>
+      <c r="AP27" s="166">
+        <v>1</v>
+      </c>
+      <c r="AQ27" s="166">
+        <v>1</v>
+      </c>
+      <c r="AR27" s="167"/>
       <c r="AS27" s="128"/>
       <c r="AT27" s="72"/>
       <c r="AU27" s="131"/>
@@ -4807,13 +4807,13 @@
     <row r="28" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="45"/>
       <c r="B28" s="46"/>
-      <c r="C28" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="206"/>
-      <c r="E28" s="206"/>
-      <c r="F28" s="206"/>
-      <c r="G28" s="207"/>
+      <c r="C28" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="233"/>
+      <c r="E28" s="233"/>
+      <c r="F28" s="233"/>
+      <c r="G28" s="234"/>
       <c r="H28" s="122"/>
       <c r="I28" s="130"/>
       <c r="J28" s="89"/>
@@ -4841,7 +4841,7 @@
       <c r="AC28" s="59"/>
       <c r="AD28" s="56"/>
       <c r="AE28" s="56"/>
-      <c r="AF28" s="208"/>
+      <c r="AF28" s="157"/>
       <c r="AG28" s="100"/>
       <c r="AH28" s="63"/>
       <c r="AI28" s="101"/>
@@ -4868,13 +4868,13 @@
     <row r="29" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="45"/>
       <c r="B29" s="87"/>
-      <c r="C29" s="219"/>
-      <c r="D29" s="210"/>
-      <c r="E29" s="252"/>
-      <c r="F29" s="182"/>
-      <c r="G29" s="253"/>
-      <c r="H29" s="221"/>
-      <c r="I29" s="246"/>
+      <c r="C29" s="168"/>
+      <c r="D29" s="159"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="134"/>
+      <c r="G29" s="201"/>
+      <c r="H29" s="170"/>
+      <c r="I29" s="195"/>
       <c r="J29" s="129"/>
       <c r="K29" s="124"/>
       <c r="L29" s="49"/>
@@ -4886,10 +4886,10 @@
       <c r="O29" s="53">
         <v>1</v>
       </c>
-      <c r="P29" s="243"/>
+      <c r="P29" s="192"/>
       <c r="Q29" s="125"/>
-      <c r="R29" s="244"/>
-      <c r="S29" s="245"/>
+      <c r="R29" s="193"/>
+      <c r="S29" s="194"/>
       <c r="T29" s="95"/>
       <c r="U29" s="56">
         <f t="shared" ref="U29" si="14">ROUND(((P29*I29)+(Q29*J29)+(R29*K29)+(S29*L29)+(T29*M29))*O29,2)</f>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="W29" s="131"/>
       <c r="X29" s="127"/>
-      <c r="Y29" s="215"/>
+      <c r="Y29" s="164"/>
       <c r="Z29" s="77"/>
       <c r="AA29" s="99"/>
       <c r="AB29" s="58" t="e">
@@ -4946,7 +4946,7 @@
         <f t="shared" ref="AN29" si="22">-((50-((176+(45+(50-AH29)))))/200)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO29" s="248"/>
+      <c r="AO29" s="197"/>
       <c r="AP29" s="69">
         <f t="shared" ref="AP29:AQ29" si="23">100%+AO29</f>
         <v>1</v>
@@ -4974,13 +4974,13 @@
     <row r="30" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A30" s="45"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="206"/>
-      <c r="E30" s="206"/>
-      <c r="F30" s="206"/>
-      <c r="G30" s="207"/>
+      <c r="C30" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="233"/>
+      <c r="E30" s="233"/>
+      <c r="F30" s="233"/>
+      <c r="G30" s="234"/>
       <c r="H30" s="122"/>
       <c r="I30" s="130"/>
       <c r="J30" s="89"/>
@@ -5008,7 +5008,7 @@
       <c r="AC30" s="59"/>
       <c r="AD30" s="56"/>
       <c r="AE30" s="56"/>
-      <c r="AF30" s="208"/>
+      <c r="AF30" s="157"/>
       <c r="AG30" s="100"/>
       <c r="AH30" s="63"/>
       <c r="AI30" s="101"/>
@@ -5035,13 +5035,13 @@
     <row r="31" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="45"/>
       <c r="B31" s="87"/>
-      <c r="C31" s="219"/>
-      <c r="D31" s="258"/>
-      <c r="E31" s="219"/>
-      <c r="F31" s="182"/>
+      <c r="C31" s="168"/>
+      <c r="D31" s="205"/>
+      <c r="E31" s="168"/>
+      <c r="F31" s="134"/>
       <c r="G31" s="103"/>
-      <c r="H31" s="211"/>
-      <c r="I31" s="246"/>
+      <c r="H31" s="160"/>
+      <c r="I31" s="195"/>
       <c r="J31" s="129"/>
       <c r="K31" s="124"/>
       <c r="L31" s="49"/>
@@ -5053,10 +5053,10 @@
       <c r="O31" s="53">
         <v>1</v>
       </c>
-      <c r="P31" s="260"/>
-      <c r="Q31" s="261"/>
-      <c r="R31" s="244"/>
-      <c r="S31" s="245"/>
+      <c r="P31" s="207"/>
+      <c r="Q31" s="208"/>
+      <c r="R31" s="193"/>
+      <c r="S31" s="194"/>
       <c r="T31" s="95"/>
       <c r="U31" s="56">
         <f t="shared" si="12"/>
@@ -5066,10 +5066,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W31" s="262"/>
+      <c r="W31" s="209"/>
       <c r="X31" s="126"/>
       <c r="Y31" s="131"/>
-      <c r="Z31" s="250"/>
+      <c r="Z31" s="199"/>
       <c r="AA31" s="99"/>
       <c r="AB31" s="58" t="e">
         <f t="shared" si="3"/>
@@ -5114,13 +5114,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO31" s="68"/>
-      <c r="AP31" s="217">
-        <v>1</v>
-      </c>
-      <c r="AQ31" s="217">
-        <v>1</v>
-      </c>
-      <c r="AR31" s="218"/>
+      <c r="AP31" s="166">
+        <v>1</v>
+      </c>
+      <c r="AQ31" s="166">
+        <v>1</v>
+      </c>
+      <c r="AR31" s="167"/>
       <c r="AS31" s="71"/>
       <c r="AT31" s="131"/>
       <c r="AU31" s="131"/>
@@ -5139,13 +5139,13 @@
     <row r="32" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="45"/>
       <c r="B32" s="46"/>
-      <c r="C32" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="206"/>
-      <c r="E32" s="206"/>
-      <c r="F32" s="206"/>
-      <c r="G32" s="207"/>
+      <c r="C32" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="233"/>
+      <c r="E32" s="233"/>
+      <c r="F32" s="233"/>
+      <c r="G32" s="234"/>
       <c r="H32" s="122"/>
       <c r="I32" s="130"/>
       <c r="J32" s="130"/>
@@ -5173,7 +5173,7 @@
       <c r="AC32" s="59"/>
       <c r="AD32" s="56"/>
       <c r="AE32" s="56"/>
-      <c r="AF32" s="208"/>
+      <c r="AF32" s="157"/>
       <c r="AG32" s="100"/>
       <c r="AH32" s="63"/>
       <c r="AI32" s="101"/>
@@ -5200,13 +5200,13 @@
     <row r="33" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="45"/>
       <c r="B33" s="87"/>
-      <c r="C33" s="219"/>
-      <c r="D33" s="210"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="249"/>
+      <c r="C33" s="168"/>
+      <c r="D33" s="159"/>
+      <c r="E33" s="200"/>
+      <c r="F33" s="198"/>
       <c r="G33" s="103"/>
-      <c r="H33" s="211"/>
-      <c r="I33" s="246"/>
+      <c r="H33" s="160"/>
+      <c r="I33" s="195"/>
       <c r="J33" s="129"/>
       <c r="K33" s="124"/>
       <c r="L33" s="49"/>
@@ -5218,7 +5218,7 @@
       <c r="O33" s="53">
         <v>1</v>
       </c>
-      <c r="P33" s="254"/>
+      <c r="P33" s="202"/>
       <c r="Q33" s="125"/>
       <c r="R33" s="125"/>
       <c r="S33" s="76"/>
@@ -5234,7 +5234,7 @@
       <c r="W33" s="131"/>
       <c r="X33" s="131"/>
       <c r="Y33" s="131"/>
-      <c r="Z33" s="247"/>
+      <c r="Z33" s="196"/>
       <c r="AA33" s="99"/>
       <c r="AB33" s="58" t="e">
         <f t="shared" si="3"/>
@@ -5279,13 +5279,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO33" s="68"/>
-      <c r="AP33" s="217">
-        <v>1</v>
-      </c>
-      <c r="AQ33" s="217">
-        <v>1</v>
-      </c>
-      <c r="AR33" s="218"/>
+      <c r="AP33" s="166">
+        <v>1</v>
+      </c>
+      <c r="AQ33" s="166">
+        <v>1</v>
+      </c>
+      <c r="AR33" s="167"/>
       <c r="AS33" s="128"/>
       <c r="AT33" s="131"/>
       <c r="AU33" s="131"/>
@@ -5304,13 +5304,13 @@
     <row r="34" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="45"/>
       <c r="B34" s="46"/>
-      <c r="C34" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="206"/>
-      <c r="E34" s="206"/>
-      <c r="F34" s="206"/>
-      <c r="G34" s="207"/>
+      <c r="C34" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="233"/>
+      <c r="E34" s="233"/>
+      <c r="F34" s="233"/>
+      <c r="G34" s="234"/>
       <c r="H34" s="122"/>
       <c r="I34" s="130"/>
       <c r="J34" s="130"/>
@@ -5338,7 +5338,7 @@
       <c r="AC34" s="59"/>
       <c r="AD34" s="56"/>
       <c r="AE34" s="56"/>
-      <c r="AF34" s="208"/>
+      <c r="AF34" s="157"/>
       <c r="AG34" s="100"/>
       <c r="AH34" s="63"/>
       <c r="AI34" s="101"/>
@@ -5365,13 +5365,13 @@
     <row r="35" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="45"/>
       <c r="B35" s="87"/>
-      <c r="C35" s="219"/>
-      <c r="D35" s="219"/>
-      <c r="E35" s="252"/>
-      <c r="F35" s="182"/>
-      <c r="G35" s="263"/>
-      <c r="H35" s="211"/>
-      <c r="I35" s="246"/>
+      <c r="C35" s="168"/>
+      <c r="D35" s="168"/>
+      <c r="E35" s="200"/>
+      <c r="F35" s="134"/>
+      <c r="G35" s="210"/>
+      <c r="H35" s="160"/>
+      <c r="I35" s="195"/>
       <c r="J35" s="129"/>
       <c r="K35" s="124"/>
       <c r="L35" s="49"/>
@@ -5383,7 +5383,7 @@
       <c r="O35" s="53">
         <v>1</v>
       </c>
-      <c r="P35" s="254"/>
+      <c r="P35" s="202"/>
       <c r="Q35" s="125"/>
       <c r="R35" s="125"/>
       <c r="S35" s="55"/>
@@ -5397,9 +5397,9 @@
         <v>0</v>
       </c>
       <c r="W35" s="131"/>
-      <c r="X35" s="215"/>
-      <c r="Y35" s="264"/>
-      <c r="Z35" s="250"/>
+      <c r="X35" s="164"/>
+      <c r="Y35" s="211"/>
+      <c r="Z35" s="199"/>
       <c r="AA35" s="99"/>
       <c r="AB35" s="58" t="e">
         <f t="shared" si="3"/>
@@ -5443,14 +5443,14 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO35" s="248"/>
-      <c r="AP35" s="217">
-        <v>2</v>
-      </c>
-      <c r="AQ35" s="217">
-        <v>1</v>
-      </c>
-      <c r="AR35" s="218"/>
+      <c r="AO35" s="197"/>
+      <c r="AP35" s="166">
+        <v>2</v>
+      </c>
+      <c r="AQ35" s="166">
+        <v>1</v>
+      </c>
+      <c r="AR35" s="167"/>
       <c r="AS35" s="71"/>
       <c r="AT35" s="131"/>
       <c r="AU35" s="131"/>
@@ -5469,13 +5469,13 @@
     <row r="36" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="45"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="206"/>
-      <c r="E36" s="206"/>
-      <c r="F36" s="206"/>
-      <c r="G36" s="207"/>
+      <c r="C36" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="233"/>
+      <c r="E36" s="233"/>
+      <c r="F36" s="233"/>
+      <c r="G36" s="234"/>
       <c r="H36" s="122"/>
       <c r="I36" s="130"/>
       <c r="J36" s="89"/>
@@ -5503,7 +5503,7 @@
       <c r="AC36" s="59"/>
       <c r="AD36" s="56"/>
       <c r="AE36" s="56"/>
-      <c r="AF36" s="208"/>
+      <c r="AF36" s="157"/>
       <c r="AG36" s="100"/>
       <c r="AH36" s="63"/>
       <c r="AI36" s="101"/>
@@ -5530,15 +5530,15 @@
     <row r="37" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="45"/>
       <c r="B37" s="87"/>
-      <c r="C37" s="252"/>
-      <c r="D37" s="210"/>
-      <c r="E37" s="258"/>
-      <c r="F37" s="184"/>
-      <c r="G37" s="253"/>
-      <c r="H37" s="211" t="s">
-        <v>66</v>
-      </c>
-      <c r="I37" s="246"/>
+      <c r="C37" s="200"/>
+      <c r="D37" s="159"/>
+      <c r="E37" s="205"/>
+      <c r="F37" s="136"/>
+      <c r="G37" s="201"/>
+      <c r="H37" s="160" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" s="195"/>
       <c r="J37" s="129"/>
       <c r="K37" s="124"/>
       <c r="L37" s="117"/>
@@ -5565,8 +5565,8 @@
       </c>
       <c r="W37" s="131"/>
       <c r="X37" s="131"/>
-      <c r="Y37" s="215"/>
-      <c r="Z37" s="250"/>
+      <c r="Y37" s="164"/>
+      <c r="Z37" s="199"/>
       <c r="AA37" s="99"/>
       <c r="AB37" s="58" t="e">
         <f t="shared" si="3"/>
@@ -5610,11 +5610,11 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO37" s="248"/>
-      <c r="AP37" s="217">
-        <v>2</v>
-      </c>
-      <c r="AQ37" s="217">
+      <c r="AO37" s="197"/>
+      <c r="AP37" s="166">
+        <v>2</v>
+      </c>
+      <c r="AQ37" s="166">
         <v>2</v>
       </c>
       <c r="AR37" s="70"/>
@@ -5636,13 +5636,13 @@
     <row r="38" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A38" s="45"/>
       <c r="B38" s="46"/>
-      <c r="C38" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="206"/>
-      <c r="E38" s="206"/>
-      <c r="F38" s="206"/>
-      <c r="G38" s="207"/>
+      <c r="C38" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="233"/>
+      <c r="E38" s="233"/>
+      <c r="F38" s="233"/>
+      <c r="G38" s="234"/>
       <c r="H38" s="122"/>
       <c r="I38" s="130"/>
       <c r="J38" s="89"/>
@@ -5670,7 +5670,7 @@
       <c r="AC38" s="59"/>
       <c r="AD38" s="56"/>
       <c r="AE38" s="56"/>
-      <c r="AF38" s="208"/>
+      <c r="AF38" s="157"/>
       <c r="AG38" s="100"/>
       <c r="AH38" s="63"/>
       <c r="AI38" s="101"/>
@@ -5697,13 +5697,13 @@
     <row r="39" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A39" s="45"/>
       <c r="B39" s="87"/>
-      <c r="C39" s="219"/>
-      <c r="D39" s="210"/>
-      <c r="E39" s="210"/>
-      <c r="F39" s="249"/>
-      <c r="G39" s="253"/>
-      <c r="H39" s="211"/>
-      <c r="I39" s="246"/>
+      <c r="C39" s="168"/>
+      <c r="D39" s="159"/>
+      <c r="E39" s="159"/>
+      <c r="F39" s="198"/>
+      <c r="G39" s="201"/>
+      <c r="H39" s="160"/>
+      <c r="I39" s="195"/>
       <c r="J39" s="129"/>
       <c r="K39" s="124"/>
       <c r="L39" s="49"/>
@@ -5715,10 +5715,10 @@
       <c r="O39" s="53">
         <v>1</v>
       </c>
-      <c r="P39" s="265"/>
-      <c r="Q39" s="266"/>
+      <c r="P39" s="212"/>
+      <c r="Q39" s="213"/>
       <c r="R39" s="125"/>
-      <c r="S39" s="267"/>
+      <c r="S39" s="214"/>
       <c r="T39" s="95"/>
       <c r="U39" s="56">
         <f t="shared" ref="U39" si="26">ROUND(((P39*I39)+(Q39*J39)+(R39*K39)+(S39*L39)+(T39*M39))*O39,2)</f>
@@ -5775,11 +5775,11 @@
         <f t="shared" ref="AN39" si="34">-((50-((176+(45+(50-AH39)))))/200)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO39" s="248"/>
-      <c r="AP39" s="217">
-        <v>2</v>
-      </c>
-      <c r="AQ39" s="217">
+      <c r="AO39" s="197"/>
+      <c r="AP39" s="166">
+        <v>2</v>
+      </c>
+      <c r="AQ39" s="166">
         <v>1</v>
       </c>
       <c r="AR39" s="70"/>
@@ -5801,13 +5801,13 @@
     <row r="40" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="45"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D40" s="206"/>
-      <c r="E40" s="206"/>
-      <c r="F40" s="206"/>
-      <c r="G40" s="207"/>
+      <c r="C40" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" s="233"/>
+      <c r="E40" s="233"/>
+      <c r="F40" s="233"/>
+      <c r="G40" s="234"/>
       <c r="H40" s="122"/>
       <c r="I40" s="130"/>
       <c r="J40" s="130"/>
@@ -5835,7 +5835,7 @@
       <c r="AC40" s="59"/>
       <c r="AD40" s="56"/>
       <c r="AE40" s="56"/>
-      <c r="AF40" s="208"/>
+      <c r="AF40" s="157"/>
       <c r="AG40" s="100"/>
       <c r="AH40" s="63"/>
       <c r="AI40" s="101"/>
@@ -5862,16 +5862,16 @@
     <row r="41" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="45"/>
       <c r="B41" s="87"/>
-      <c r="C41" s="219"/>
-      <c r="D41" s="252"/>
+      <c r="C41" s="168"/>
+      <c r="D41" s="200"/>
       <c r="E41" s="115"/>
       <c r="F41" s="115" t="s">
-        <v>67</v>
-      </c>
-      <c r="G41" s="221"/>
-      <c r="H41" s="211"/>
+        <v>66</v>
+      </c>
+      <c r="G41" s="170"/>
+      <c r="H41" s="160"/>
       <c r="I41" s="124"/>
-      <c r="J41" s="268"/>
+      <c r="J41" s="215"/>
       <c r="K41" s="50"/>
       <c r="L41" s="50"/>
       <c r="M41" s="104"/>
@@ -5882,10 +5882,10 @@
       <c r="O41" s="53">
         <v>1</v>
       </c>
-      <c r="P41" s="254"/>
+      <c r="P41" s="202"/>
       <c r="Q41" s="125"/>
       <c r="R41" s="55"/>
-      <c r="S41" s="245"/>
+      <c r="S41" s="194"/>
       <c r="T41" s="95"/>
       <c r="U41" s="56">
         <f t="shared" ref="U41" si="37">ROUND(((P41*I41)+(Q41*J41)+(R41*K41)+(S41*L41)+(T41*M41))*O41,2)</f>
@@ -5895,8 +5895,8 @@
         <f t="shared" ref="V41" si="38">IF(U41&gt;=15,15,U41)</f>
         <v>0</v>
       </c>
-      <c r="W41" s="269"/>
-      <c r="X41" s="270"/>
+      <c r="W41" s="216"/>
+      <c r="X41" s="217"/>
       <c r="Y41" s="106"/>
       <c r="Z41" s="57"/>
       <c r="AA41" s="99"/>
@@ -5951,7 +5951,7 @@
         <f t="shared" si="46"/>
         <v>2</v>
       </c>
-      <c r="AR41" s="218"/>
+      <c r="AR41" s="167"/>
       <c r="AS41" s="71"/>
       <c r="AT41" s="131"/>
       <c r="AU41" s="131"/>
@@ -5970,13 +5970,13 @@
     <row r="42" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="45"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D42" s="206"/>
-      <c r="E42" s="206"/>
-      <c r="F42" s="206"/>
-      <c r="G42" s="207"/>
+      <c r="C42" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="233"/>
+      <c r="E42" s="233"/>
+      <c r="F42" s="233"/>
+      <c r="G42" s="234"/>
       <c r="H42" s="122"/>
       <c r="I42" s="89"/>
       <c r="J42" s="130"/>
@@ -6004,7 +6004,7 @@
       <c r="AC42" s="59"/>
       <c r="AD42" s="56"/>
       <c r="AE42" s="56"/>
-      <c r="AF42" s="208"/>
+      <c r="AF42" s="157"/>
       <c r="AG42" s="100"/>
       <c r="AH42" s="63"/>
       <c r="AI42" s="101"/>
@@ -6031,12 +6031,12 @@
     <row r="43" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A43" s="45"/>
       <c r="B43" s="87"/>
-      <c r="C43" s="182"/>
-      <c r="D43" s="252"/>
-      <c r="E43" s="252"/>
-      <c r="F43" s="182"/>
+      <c r="C43" s="134"/>
+      <c r="D43" s="200"/>
+      <c r="E43" s="200"/>
+      <c r="F43" s="134"/>
       <c r="G43" s="103"/>
-      <c r="H43" s="211"/>
+      <c r="H43" s="160"/>
       <c r="I43" s="48"/>
       <c r="J43" s="124"/>
       <c r="K43" s="124"/>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="W43" s="88"/>
       <c r="X43" s="131"/>
-      <c r="Y43" s="271"/>
+      <c r="Y43" s="218"/>
       <c r="Z43" s="88"/>
       <c r="AA43" s="99"/>
       <c r="AB43" s="58" t="e">
@@ -6113,7 +6113,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO43" s="68"/>
-      <c r="AP43" s="217">
+      <c r="AP43" s="166">
         <v>1</v>
       </c>
       <c r="AQ43" s="69">
@@ -6139,13 +6139,13 @@
     <row r="44" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A44" s="45"/>
       <c r="B44" s="46"/>
-      <c r="C44" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" s="206"/>
-      <c r="E44" s="206"/>
-      <c r="F44" s="206"/>
-      <c r="G44" s="207"/>
+      <c r="C44" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="233"/>
+      <c r="E44" s="233"/>
+      <c r="F44" s="233"/>
+      <c r="G44" s="234"/>
       <c r="H44" s="122"/>
       <c r="I44" s="130"/>
       <c r="J44" s="130"/>
@@ -6173,7 +6173,7 @@
       <c r="AC44" s="59"/>
       <c r="AD44" s="56"/>
       <c r="AE44" s="56"/>
-      <c r="AF44" s="208"/>
+      <c r="AF44" s="157"/>
       <c r="AG44" s="100"/>
       <c r="AH44" s="63"/>
       <c r="AI44" s="101"/>
@@ -6200,12 +6200,12 @@
     <row r="45" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A45" s="45"/>
       <c r="B45" s="87"/>
-      <c r="C45" s="182"/>
-      <c r="D45" s="210"/>
-      <c r="E45" s="252"/>
-      <c r="F45" s="184"/>
+      <c r="C45" s="134"/>
+      <c r="D45" s="159"/>
+      <c r="E45" s="200"/>
+      <c r="F45" s="136"/>
       <c r="G45" s="103"/>
-      <c r="H45" s="211"/>
+      <c r="H45" s="160"/>
       <c r="I45" s="48"/>
       <c r="J45" s="124"/>
       <c r="K45" s="124"/>
@@ -6221,7 +6221,7 @@
       <c r="P45" s="54"/>
       <c r="Q45" s="125"/>
       <c r="R45" s="125"/>
-      <c r="S45" s="245"/>
+      <c r="S45" s="194"/>
       <c r="T45" s="95"/>
       <c r="U45" s="56">
         <f t="shared" si="12"/>
@@ -6231,10 +6231,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W45" s="250"/>
+      <c r="W45" s="199"/>
       <c r="X45" s="131"/>
       <c r="Y45" s="126"/>
-      <c r="Z45" s="250"/>
+      <c r="Z45" s="199"/>
       <c r="AA45" s="99"/>
       <c r="AB45" s="58" t="e">
         <f t="shared" si="3"/>
@@ -6251,7 +6251,7 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF45" s="216"/>
+      <c r="AF45" s="165"/>
       <c r="AG45" s="62"/>
       <c r="AH45" s="63" t="e">
         <f t="shared" si="6"/>
@@ -6279,7 +6279,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO45" s="68"/>
-      <c r="AP45" s="217">
+      <c r="AP45" s="166">
         <v>1</v>
       </c>
       <c r="AQ45" s="69">
@@ -6305,13 +6305,13 @@
     <row r="46" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="45"/>
       <c r="B46" s="87"/>
-      <c r="C46" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" s="206"/>
-      <c r="E46" s="206"/>
-      <c r="F46" s="206"/>
-      <c r="G46" s="207"/>
+      <c r="C46" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" s="233"/>
+      <c r="E46" s="233"/>
+      <c r="F46" s="233"/>
+      <c r="G46" s="234"/>
       <c r="H46" s="122"/>
       <c r="I46" s="89"/>
       <c r="J46" s="130"/>
@@ -6339,7 +6339,7 @@
       <c r="AC46" s="59"/>
       <c r="AD46" s="56"/>
       <c r="AE46" s="56"/>
-      <c r="AF46" s="208"/>
+      <c r="AF46" s="157"/>
       <c r="AG46" s="100"/>
       <c r="AH46" s="63"/>
       <c r="AI46" s="101"/>
@@ -6366,13 +6366,13 @@
     <row r="47" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="45"/>
       <c r="B47" s="87"/>
-      <c r="C47" s="252"/>
-      <c r="D47" s="252"/>
-      <c r="E47" s="252"/>
-      <c r="F47" s="184"/>
+      <c r="C47" s="200"/>
+      <c r="D47" s="200"/>
+      <c r="E47" s="200"/>
+      <c r="F47" s="136"/>
       <c r="G47" s="103"/>
-      <c r="H47" s="211"/>
-      <c r="I47" s="246"/>
+      <c r="H47" s="160"/>
+      <c r="I47" s="195"/>
       <c r="J47" s="124"/>
       <c r="K47" s="124"/>
       <c r="L47" s="49"/>
@@ -6385,9 +6385,9 @@
         <v>1</v>
       </c>
       <c r="P47" s="107"/>
-      <c r="Q47" s="244"/>
-      <c r="R47" s="244"/>
-      <c r="S47" s="245"/>
+      <c r="Q47" s="193"/>
+      <c r="R47" s="193"/>
+      <c r="S47" s="194"/>
       <c r="T47" s="95"/>
       <c r="U47" s="56">
         <f t="shared" si="12"/>
@@ -6400,7 +6400,7 @@
       <c r="W47" s="131"/>
       <c r="X47" s="131"/>
       <c r="Y47" s="131"/>
-      <c r="Z47" s="272"/>
+      <c r="Z47" s="219"/>
       <c r="AA47" s="99"/>
       <c r="AB47" s="58" t="e">
         <f t="shared" si="3"/>
@@ -6449,7 +6449,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AQ47" s="217">
+      <c r="AQ47" s="166">
         <v>1</v>
       </c>
       <c r="AR47" s="70"/>
@@ -6471,13 +6471,13 @@
     <row r="48" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A48" s="45"/>
       <c r="B48" s="46"/>
-      <c r="C48" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" s="206"/>
-      <c r="E48" s="206"/>
-      <c r="F48" s="206"/>
-      <c r="G48" s="207"/>
+      <c r="C48" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" s="233"/>
+      <c r="E48" s="233"/>
+      <c r="F48" s="233"/>
+      <c r="G48" s="234"/>
       <c r="H48" s="122"/>
       <c r="I48" s="89"/>
       <c r="J48" s="130"/>
@@ -6505,7 +6505,7 @@
       <c r="AC48" s="59"/>
       <c r="AD48" s="56"/>
       <c r="AE48" s="56"/>
-      <c r="AF48" s="208"/>
+      <c r="AF48" s="157"/>
       <c r="AG48" s="100"/>
       <c r="AH48" s="63"/>
       <c r="AI48" s="101"/>
@@ -6532,13 +6532,13 @@
     <row r="49" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A49" s="45"/>
       <c r="B49" s="87"/>
-      <c r="C49" s="219"/>
-      <c r="D49" s="219"/>
-      <c r="E49" s="258"/>
-      <c r="F49" s="209"/>
-      <c r="G49" s="253"/>
-      <c r="H49" s="221"/>
-      <c r="I49" s="246"/>
+      <c r="C49" s="168"/>
+      <c r="D49" s="168"/>
+      <c r="E49" s="205"/>
+      <c r="F49" s="158"/>
+      <c r="G49" s="201"/>
+      <c r="H49" s="170"/>
+      <c r="I49" s="195"/>
       <c r="J49" s="124"/>
       <c r="K49" s="124"/>
       <c r="L49" s="49"/>
@@ -6550,10 +6550,10 @@
       <c r="O49" s="53">
         <v>1</v>
       </c>
-      <c r="P49" s="243"/>
-      <c r="Q49" s="244"/>
-      <c r="R49" s="244"/>
-      <c r="S49" s="245"/>
+      <c r="P49" s="192"/>
+      <c r="Q49" s="193"/>
+      <c r="R49" s="193"/>
+      <c r="S49" s="194"/>
       <c r="T49" s="95"/>
       <c r="U49" s="56">
         <f t="shared" si="12"/>
@@ -6563,10 +6563,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W49" s="262"/>
-      <c r="X49" s="215"/>
-      <c r="Y49" s="234"/>
-      <c r="Z49" s="272"/>
+      <c r="W49" s="209"/>
+      <c r="X49" s="164"/>
+      <c r="Y49" s="183"/>
+      <c r="Z49" s="219"/>
       <c r="AA49" s="99"/>
       <c r="AB49" s="58" t="e">
         <f t="shared" si="3"/>
@@ -6610,11 +6610,11 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO49" s="248"/>
-      <c r="AP49" s="217">
-        <v>1</v>
-      </c>
-      <c r="AQ49" s="217">
+      <c r="AO49" s="197"/>
+      <c r="AP49" s="166">
+        <v>1</v>
+      </c>
+      <c r="AQ49" s="166">
         <v>1</v>
       </c>
       <c r="AR49" s="70"/>
@@ -6636,13 +6636,13 @@
     <row r="50" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A50" s="45"/>
       <c r="B50" s="46"/>
-      <c r="C50" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="206"/>
-      <c r="E50" s="206"/>
-      <c r="F50" s="206"/>
-      <c r="G50" s="207"/>
+      <c r="C50" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50" s="233"/>
+      <c r="E50" s="233"/>
+      <c r="F50" s="233"/>
+      <c r="G50" s="234"/>
       <c r="H50" s="122"/>
       <c r="I50" s="89"/>
       <c r="J50" s="130"/>
@@ -6670,7 +6670,7 @@
       <c r="AC50" s="59"/>
       <c r="AD50" s="56"/>
       <c r="AE50" s="56"/>
-      <c r="AF50" s="208"/>
+      <c r="AF50" s="157"/>
       <c r="AG50" s="100"/>
       <c r="AH50" s="63"/>
       <c r="AI50" s="101"/>
@@ -6697,13 +6697,13 @@
     <row r="51" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A51" s="45"/>
       <c r="B51" s="87"/>
-      <c r="C51" s="219"/>
-      <c r="D51" s="210"/>
-      <c r="E51" s="252"/>
+      <c r="C51" s="168"/>
+      <c r="D51" s="159"/>
+      <c r="E51" s="200"/>
       <c r="F51" s="114"/>
       <c r="G51" s="103"/>
-      <c r="H51" s="211"/>
-      <c r="I51" s="246"/>
+      <c r="H51" s="160"/>
+      <c r="I51" s="195"/>
       <c r="J51" s="124"/>
       <c r="K51" s="124"/>
       <c r="L51" s="49"/>
@@ -6715,9 +6715,9 @@
       <c r="O51" s="53">
         <v>1</v>
       </c>
-      <c r="P51" s="254"/>
+      <c r="P51" s="202"/>
       <c r="Q51" s="125"/>
-      <c r="R51" s="244"/>
+      <c r="R51" s="193"/>
       <c r="S51" s="76"/>
       <c r="T51" s="95"/>
       <c r="U51" s="56">
@@ -6728,10 +6728,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W51" s="262"/>
+      <c r="W51" s="209"/>
       <c r="X51" s="131"/>
       <c r="Y51" s="131"/>
-      <c r="Z51" s="250"/>
+      <c r="Z51" s="199"/>
       <c r="AA51" s="99"/>
       <c r="AB51" s="58" t="e">
         <f t="shared" si="3"/>
@@ -6775,8 +6775,8 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO51" s="248"/>
-      <c r="AP51" s="217"/>
+      <c r="AO51" s="197"/>
+      <c r="AP51" s="166"/>
       <c r="AQ51" s="69">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -6800,13 +6800,13 @@
     <row r="52" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A52" s="45"/>
       <c r="B52" s="46"/>
-      <c r="C52" s="205" t="s">
-        <v>68</v>
-      </c>
-      <c r="D52" s="206"/>
-      <c r="E52" s="206"/>
-      <c r="F52" s="206"/>
-      <c r="G52" s="207"/>
+      <c r="C52" s="232" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="233"/>
+      <c r="E52" s="233"/>
+      <c r="F52" s="233"/>
+      <c r="G52" s="234"/>
       <c r="H52" s="122"/>
       <c r="I52" s="89"/>
       <c r="J52" s="130"/>
@@ -6834,7 +6834,7 @@
       <c r="AC52" s="59"/>
       <c r="AD52" s="56"/>
       <c r="AE52" s="56"/>
-      <c r="AF52" s="208"/>
+      <c r="AF52" s="157"/>
       <c r="AG52" s="100"/>
       <c r="AH52" s="63"/>
       <c r="AI52" s="101"/>
@@ -6861,13 +6861,13 @@
     <row r="53" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A53" s="45"/>
       <c r="B53" s="87"/>
-      <c r="C53" s="219"/>
-      <c r="D53" s="219"/>
-      <c r="E53" s="252"/>
-      <c r="F53" s="249"/>
+      <c r="C53" s="168"/>
+      <c r="D53" s="168"/>
+      <c r="E53" s="200"/>
+      <c r="F53" s="198"/>
       <c r="G53" s="103"/>
-      <c r="H53" s="211"/>
-      <c r="I53" s="246"/>
+      <c r="H53" s="160"/>
+      <c r="I53" s="195"/>
       <c r="J53" s="129"/>
       <c r="K53" s="124"/>
       <c r="L53" s="49"/>
@@ -6879,7 +6879,7 @@
       <c r="O53" s="53">
         <v>1</v>
       </c>
-      <c r="P53" s="254"/>
+      <c r="P53" s="202"/>
       <c r="Q53" s="125"/>
       <c r="R53" s="125"/>
       <c r="S53" s="76"/>
@@ -6893,9 +6893,9 @@
         <v>0</v>
       </c>
       <c r="W53" s="126"/>
-      <c r="X53" s="271"/>
+      <c r="X53" s="218"/>
       <c r="Y53" s="126"/>
-      <c r="Z53" s="271"/>
+      <c r="Z53" s="218"/>
       <c r="AA53" s="99"/>
       <c r="AB53" s="58" t="e">
         <f t="shared" ref="AB53" si="53">ROUND((((W53*I53)+(X53*J53)+(Y53*K53)+(Z53*L53)+(AA53*M53))/$I$2),2)*13</f>
@@ -6939,11 +6939,11 @@
         <f t="shared" ref="AN53" si="59">-((50-((176+(45+(50-AH53)))))/200)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO53" s="248"/>
-      <c r="AP53" s="217">
-        <v>1</v>
-      </c>
-      <c r="AQ53" s="217">
+      <c r="AO53" s="197"/>
+      <c r="AP53" s="166">
+        <v>1</v>
+      </c>
+      <c r="AQ53" s="166">
         <v>1</v>
       </c>
       <c r="AR53" s="70"/>
@@ -6965,15 +6965,15 @@
     <row r="54" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A54" s="45"/>
       <c r="B54" s="46"/>
-      <c r="C54" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D54" s="206"/>
-      <c r="E54" s="206"/>
-      <c r="F54" s="206"/>
-      <c r="G54" s="207"/>
+      <c r="C54" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" s="233"/>
+      <c r="E54" s="233"/>
+      <c r="F54" s="233"/>
+      <c r="G54" s="234"/>
       <c r="H54" s="122"/>
-      <c r="I54" s="273"/>
+      <c r="I54" s="220"/>
       <c r="J54" s="89"/>
       <c r="K54" s="89"/>
       <c r="L54" s="89"/>
@@ -6999,7 +6999,7 @@
       <c r="AC54" s="59"/>
       <c r="AD54" s="56"/>
       <c r="AE54" s="56"/>
-      <c r="AF54" s="208"/>
+      <c r="AF54" s="157"/>
       <c r="AG54" s="100"/>
       <c r="AH54" s="63"/>
       <c r="AI54" s="101"/>
@@ -7026,12 +7026,12 @@
     <row r="55" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A55" s="45"/>
       <c r="B55" s="87"/>
-      <c r="C55" s="252"/>
-      <c r="D55" s="252"/>
-      <c r="E55" s="252"/>
-      <c r="F55" s="249"/>
+      <c r="C55" s="200"/>
+      <c r="D55" s="200"/>
+      <c r="E55" s="200"/>
+      <c r="F55" s="198"/>
       <c r="G55" s="103"/>
-      <c r="H55" s="211"/>
+      <c r="H55" s="160"/>
       <c r="I55" s="48"/>
       <c r="J55" s="124"/>
       <c r="K55" s="124"/>
@@ -7047,7 +7047,7 @@
       <c r="P55" s="54"/>
       <c r="Q55" s="125"/>
       <c r="R55" s="125"/>
-      <c r="S55" s="245"/>
+      <c r="S55" s="194"/>
       <c r="T55" s="95"/>
       <c r="U55" s="56">
         <f t="shared" si="12"/>
@@ -7058,8 +7058,8 @@
         <v>0</v>
       </c>
       <c r="W55" s="131"/>
-      <c r="X55" s="234"/>
-      <c r="Y55" s="234"/>
+      <c r="X55" s="183"/>
+      <c r="Y55" s="183"/>
       <c r="Z55" s="88"/>
       <c r="AA55" s="99"/>
       <c r="AB55" s="58" t="e">
@@ -7105,10 +7105,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO55" s="68"/>
-      <c r="AP55" s="217">
-        <v>2</v>
-      </c>
-      <c r="AQ55" s="217">
+      <c r="AP55" s="166">
+        <v>2</v>
+      </c>
+      <c r="AQ55" s="166">
         <v>3</v>
       </c>
       <c r="AR55" s="70"/>
@@ -7130,15 +7130,15 @@
     <row r="56" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A56" s="45"/>
       <c r="B56" s="46"/>
-      <c r="C56" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D56" s="206"/>
-      <c r="E56" s="206"/>
-      <c r="F56" s="206"/>
-      <c r="G56" s="207"/>
+      <c r="C56" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D56" s="233"/>
+      <c r="E56" s="233"/>
+      <c r="F56" s="233"/>
+      <c r="G56" s="234"/>
       <c r="H56" s="122"/>
-      <c r="I56" s="273"/>
+      <c r="I56" s="220"/>
       <c r="J56" s="89"/>
       <c r="K56" s="89"/>
       <c r="L56" s="89"/>
@@ -7164,7 +7164,7 @@
       <c r="AC56" s="59"/>
       <c r="AD56" s="56"/>
       <c r="AE56" s="56"/>
-      <c r="AF56" s="208"/>
+      <c r="AF56" s="157"/>
       <c r="AG56" s="100"/>
       <c r="AH56" s="63"/>
       <c r="AI56" s="101"/>
@@ -7191,13 +7191,13 @@
     <row r="57" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A57" s="45"/>
       <c r="B57" s="87"/>
-      <c r="C57" s="252"/>
-      <c r="D57" s="252"/>
-      <c r="E57" s="252"/>
-      <c r="F57" s="249"/>
+      <c r="C57" s="200"/>
+      <c r="D57" s="200"/>
+      <c r="E57" s="200"/>
+      <c r="F57" s="198"/>
       <c r="G57" s="103"/>
-      <c r="H57" s="211"/>
-      <c r="I57" s="246"/>
+      <c r="H57" s="160"/>
+      <c r="I57" s="195"/>
       <c r="J57" s="124"/>
       <c r="K57" s="124"/>
       <c r="L57" s="49"/>
@@ -7209,9 +7209,9 @@
       <c r="O57" s="53">
         <v>1</v>
       </c>
-      <c r="P57" s="254"/>
+      <c r="P57" s="202"/>
       <c r="Q57" s="125"/>
-      <c r="R57" s="259"/>
+      <c r="R57" s="206"/>
       <c r="S57" s="76"/>
       <c r="T57" s="95"/>
       <c r="U57" s="56">
@@ -7222,9 +7222,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W57" s="262"/>
+      <c r="W57" s="209"/>
       <c r="X57" s="131"/>
-      <c r="Y57" s="234"/>
+      <c r="Y57" s="183"/>
       <c r="Z57" s="88"/>
       <c r="AA57" s="99"/>
       <c r="AB57" s="58" t="e">
@@ -7269,9 +7269,9 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO57" s="248"/>
-      <c r="AP57" s="217"/>
-      <c r="AQ57" s="217">
+      <c r="AO57" s="197"/>
+      <c r="AP57" s="166"/>
+      <c r="AQ57" s="166">
         <v>2</v>
       </c>
       <c r="AR57" s="70"/>
@@ -7293,15 +7293,15 @@
     <row r="58" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A58" s="45"/>
       <c r="B58" s="46"/>
-      <c r="C58" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D58" s="206"/>
-      <c r="E58" s="206"/>
-      <c r="F58" s="206"/>
-      <c r="G58" s="207"/>
+      <c r="C58" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D58" s="233"/>
+      <c r="E58" s="233"/>
+      <c r="F58" s="233"/>
+      <c r="G58" s="234"/>
       <c r="H58" s="122"/>
-      <c r="I58" s="273"/>
+      <c r="I58" s="220"/>
       <c r="J58" s="89"/>
       <c r="K58" s="89"/>
       <c r="L58" s="89"/>
@@ -7327,7 +7327,7 @@
       <c r="AC58" s="59"/>
       <c r="AD58" s="56"/>
       <c r="AE58" s="56"/>
-      <c r="AF58" s="208"/>
+      <c r="AF58" s="157"/>
       <c r="AG58" s="100"/>
       <c r="AH58" s="63"/>
       <c r="AI58" s="101"/>
@@ -7354,17 +7354,17 @@
     <row r="59" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A59" s="45"/>
       <c r="B59" s="87"/>
-      <c r="C59" s="219"/>
-      <c r="D59" s="219"/>
-      <c r="E59" s="219"/>
-      <c r="F59" s="219"/>
+      <c r="C59" s="168"/>
+      <c r="D59" s="168"/>
+      <c r="E59" s="168"/>
+      <c r="F59" s="168"/>
       <c r="G59" s="103"/>
-      <c r="H59" s="274"/>
-      <c r="I59" s="246"/>
+      <c r="H59" s="221"/>
+      <c r="I59" s="195"/>
       <c r="J59" s="129"/>
       <c r="K59" s="50"/>
-      <c r="L59" s="212"/>
-      <c r="M59" s="226"/>
+      <c r="L59" s="161"/>
+      <c r="M59" s="175"/>
       <c r="N59" s="78">
         <f>SUM(I59:M59)</f>
         <v>0</v>
@@ -7372,11 +7372,11 @@
       <c r="O59" s="53">
         <v>1</v>
       </c>
-      <c r="P59" s="254"/>
-      <c r="Q59" s="244"/>
+      <c r="P59" s="202"/>
+      <c r="Q59" s="193"/>
       <c r="R59" s="55"/>
-      <c r="S59" s="213"/>
-      <c r="T59" s="232"/>
+      <c r="S59" s="162"/>
+      <c r="T59" s="181"/>
       <c r="U59" s="79">
         <f>ROUND(((P59*I59)+(Q59*J59)+(R59*K59)+(S59*L59)+(T59*M59))*O59,2)</f>
         <v>0</v>
@@ -7386,7 +7386,7 @@
         <v>0</v>
       </c>
       <c r="W59" s="126"/>
-      <c r="X59" s="275"/>
+      <c r="X59" s="222"/>
       <c r="Y59" s="126"/>
       <c r="Z59" s="126"/>
       <c r="AA59" s="99"/>
@@ -7433,12 +7433,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AO59" s="68"/>
-      <c r="AP59" s="217"/>
+      <c r="AP59" s="166"/>
       <c r="AQ59" s="69">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AR59" s="218"/>
+      <c r="AR59" s="167"/>
       <c r="AS59" s="71"/>
       <c r="AT59" s="131"/>
       <c r="AU59" s="72"/>
@@ -7457,15 +7457,15 @@
     <row r="60" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A60" s="45"/>
       <c r="B60" s="46"/>
-      <c r="C60" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D60" s="206"/>
-      <c r="E60" s="206"/>
-      <c r="F60" s="206"/>
-      <c r="G60" s="207"/>
+      <c r="C60" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D60" s="233"/>
+      <c r="E60" s="233"/>
+      <c r="F60" s="233"/>
+      <c r="G60" s="234"/>
       <c r="H60" s="122"/>
-      <c r="I60" s="273"/>
+      <c r="I60" s="220"/>
       <c r="J60" s="89"/>
       <c r="K60" s="89"/>
       <c r="L60" s="89"/>
@@ -7491,7 +7491,7 @@
       <c r="AC60" s="59"/>
       <c r="AD60" s="56"/>
       <c r="AE60" s="56"/>
-      <c r="AF60" s="208"/>
+      <c r="AF60" s="157"/>
       <c r="AG60" s="100"/>
       <c r="AH60" s="63"/>
       <c r="AI60" s="101"/>
@@ -7518,16 +7518,16 @@
     <row r="61" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A61" s="45"/>
       <c r="B61" s="46"/>
-      <c r="C61" s="219"/>
-      <c r="D61" s="252"/>
-      <c r="E61" s="219"/>
-      <c r="F61" s="219"/>
-      <c r="G61" s="252"/>
-      <c r="H61" s="211"/>
+      <c r="C61" s="168"/>
+      <c r="D61" s="200"/>
+      <c r="E61" s="168"/>
+      <c r="F61" s="168"/>
+      <c r="G61" s="200"/>
+      <c r="H61" s="160"/>
       <c r="I61" s="124"/>
       <c r="J61" s="50"/>
       <c r="K61" s="124"/>
-      <c r="L61" s="212"/>
+      <c r="L61" s="161"/>
       <c r="M61" s="51"/>
       <c r="N61" s="102">
         <f t="shared" ref="N61:N63" si="61">SUM(I61:M61)</f>
@@ -7536,10 +7536,10 @@
       <c r="O61" s="53">
         <v>1</v>
       </c>
-      <c r="P61" s="254"/>
+      <c r="P61" s="202"/>
       <c r="Q61" s="55"/>
-      <c r="R61" s="259"/>
-      <c r="S61" s="213"/>
+      <c r="R61" s="206"/>
+      <c r="S61" s="162"/>
       <c r="T61" s="95"/>
       <c r="U61" s="56">
         <f t="shared" si="12"/>
@@ -7552,7 +7552,7 @@
       <c r="W61" s="126"/>
       <c r="X61" s="131"/>
       <c r="Y61" s="131"/>
-      <c r="Z61" s="215"/>
+      <c r="Z61" s="164"/>
       <c r="AA61" s="99"/>
       <c r="AB61" s="58" t="e">
         <f t="shared" si="3"/>
@@ -7601,8 +7601,8 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AQ61" s="217"/>
-      <c r="AR61" s="218">
+      <c r="AQ61" s="166"/>
+      <c r="AR61" s="167">
         <v>2</v>
       </c>
       <c r="AS61" s="71"/>
@@ -7623,15 +7623,15 @@
     <row r="62" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A62" s="45"/>
       <c r="B62" s="46"/>
-      <c r="C62" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D62" s="206"/>
-      <c r="E62" s="206"/>
-      <c r="F62" s="206"/>
-      <c r="G62" s="207"/>
+      <c r="C62" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D62" s="233"/>
+      <c r="E62" s="233"/>
+      <c r="F62" s="233"/>
+      <c r="G62" s="234"/>
       <c r="H62" s="122"/>
-      <c r="I62" s="273"/>
+      <c r="I62" s="220"/>
       <c r="J62" s="89"/>
       <c r="K62" s="89"/>
       <c r="L62" s="89"/>
@@ -7657,7 +7657,7 @@
       <c r="AC62" s="59"/>
       <c r="AD62" s="56"/>
       <c r="AE62" s="56"/>
-      <c r="AF62" s="208"/>
+      <c r="AF62" s="157"/>
       <c r="AG62" s="100"/>
       <c r="AH62" s="63"/>
       <c r="AI62" s="101"/>
@@ -7685,15 +7685,15 @@
       <c r="A63" s="45"/>
       <c r="B63" s="46"/>
       <c r="C63" s="115"/>
-      <c r="D63" s="219"/>
-      <c r="E63" s="210"/>
-      <c r="F63" s="252"/>
-      <c r="G63" s="252"/>
-      <c r="H63" s="211"/>
+      <c r="D63" s="168"/>
+      <c r="E63" s="159"/>
+      <c r="F63" s="200"/>
+      <c r="G63" s="200"/>
+      <c r="H63" s="160"/>
       <c r="I63" s="50"/>
       <c r="J63" s="124"/>
       <c r="K63" s="124"/>
-      <c r="L63" s="268"/>
+      <c r="L63" s="215"/>
       <c r="M63" s="51"/>
       <c r="N63" s="102">
         <f t="shared" si="61"/>
@@ -7704,8 +7704,8 @@
       </c>
       <c r="P63" s="54"/>
       <c r="Q63" s="125"/>
-      <c r="R63" s="259"/>
-      <c r="S63" s="213"/>
+      <c r="R63" s="206"/>
+      <c r="S63" s="162"/>
       <c r="T63" s="95"/>
       <c r="U63" s="56">
         <f t="shared" si="12"/>
@@ -7715,9 +7715,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W63" s="250"/>
+      <c r="W63" s="199"/>
       <c r="X63" s="126"/>
-      <c r="Y63" s="234"/>
+      <c r="Y63" s="183"/>
       <c r="Z63" s="127"/>
       <c r="AA63" s="99"/>
       <c r="AB63" s="58" t="e">
@@ -7790,15 +7790,15 @@
     <row r="64" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A64" s="45"/>
       <c r="B64" s="46"/>
-      <c r="C64" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D64" s="206"/>
-      <c r="E64" s="206"/>
-      <c r="F64" s="206"/>
-      <c r="G64" s="207"/>
+      <c r="C64" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D64" s="233"/>
+      <c r="E64" s="233"/>
+      <c r="F64" s="233"/>
+      <c r="G64" s="234"/>
       <c r="H64" s="122"/>
-      <c r="I64" s="273"/>
+      <c r="I64" s="220"/>
       <c r="J64" s="89"/>
       <c r="K64" s="89"/>
       <c r="L64" s="89"/>
@@ -7824,7 +7824,7 @@
       <c r="AC64" s="59"/>
       <c r="AD64" s="56"/>
       <c r="AE64" s="56"/>
-      <c r="AF64" s="208"/>
+      <c r="AF64" s="157"/>
       <c r="AG64" s="100"/>
       <c r="AH64" s="63"/>
       <c r="AI64" s="101"/>
@@ -7851,12 +7851,12 @@
     <row r="65" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A65" s="87"/>
       <c r="B65" s="46"/>
-      <c r="C65" s="276"/>
+      <c r="C65" s="223"/>
       <c r="D65" s="87"/>
-      <c r="E65" s="277"/>
-      <c r="F65" s="278"/>
-      <c r="G65" s="278"/>
-      <c r="H65" s="211"/>
+      <c r="E65" s="224"/>
+      <c r="F65" s="225"/>
+      <c r="G65" s="225"/>
+      <c r="H65" s="160"/>
       <c r="I65" s="48"/>
       <c r="J65" s="50"/>
       <c r="K65" s="50"/>
@@ -7872,7 +7872,7 @@
       <c r="P65" s="92"/>
       <c r="Q65" s="93"/>
       <c r="R65" s="93"/>
-      <c r="S65" s="267"/>
+      <c r="S65" s="214"/>
       <c r="T65" s="95"/>
       <c r="U65" s="56">
         <f>ROUND(((P65*I65)+(Q65*J65)+(R65*K65)+(S65*L65)+(T65*M65))*O65,2)</f>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="W65" s="110"/>
       <c r="X65" s="88"/>
-      <c r="Y65" s="275"/>
+      <c r="Y65" s="222"/>
       <c r="Z65" s="126"/>
       <c r="AA65" s="99"/>
       <c r="AB65" s="58" t="e">
@@ -7957,15 +7957,15 @@
     <row r="66" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A66" s="45"/>
       <c r="B66" s="46"/>
-      <c r="C66" s="205" t="s">
-        <v>64</v>
-      </c>
-      <c r="D66" s="206"/>
-      <c r="E66" s="206"/>
-      <c r="F66" s="206"/>
-      <c r="G66" s="207"/>
+      <c r="C66" s="232" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" s="233"/>
+      <c r="E66" s="233"/>
+      <c r="F66" s="233"/>
+      <c r="G66" s="234"/>
       <c r="H66" s="122"/>
-      <c r="I66" s="273"/>
+      <c r="I66" s="220"/>
       <c r="J66" s="89"/>
       <c r="K66" s="89"/>
       <c r="L66" s="89"/>
@@ -7991,7 +7991,7 @@
       <c r="AC66" s="59"/>
       <c r="AD66" s="56"/>
       <c r="AE66" s="56"/>
-      <c r="AF66" s="208"/>
+      <c r="AF66" s="157"/>
       <c r="AG66" s="100"/>
       <c r="AH66" s="63"/>
       <c r="AI66" s="101"/>
@@ -8018,12 +8018,12 @@
     <row r="67" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A67" s="45"/>
       <c r="B67" s="87"/>
-      <c r="C67" s="279"/>
+      <c r="C67" s="226"/>
       <c r="D67" s="87"/>
-      <c r="E67" s="278"/>
-      <c r="F67" s="278"/>
-      <c r="G67" s="277"/>
-      <c r="H67" s="211"/>
+      <c r="E67" s="225"/>
+      <c r="F67" s="225"/>
+      <c r="G67" s="224"/>
+      <c r="H67" s="160"/>
       <c r="I67" s="48"/>
       <c r="J67" s="50"/>
       <c r="K67" s="50"/>
@@ -8039,7 +8039,7 @@
       <c r="P67" s="107"/>
       <c r="Q67" s="108"/>
       <c r="R67" s="108"/>
-      <c r="S67" s="245"/>
+      <c r="S67" s="194"/>
       <c r="T67" s="95"/>
       <c r="U67" s="56">
         <f>ROUND(((P67*I67)+(Q67*J67)+(R67*K67)+(S67*L67)+(T67*M67))*O67,2)</f>
@@ -8049,10 +8049,10 @@
         <f>IF(U67&gt;=15,15,U67)</f>
         <v>0</v>
       </c>
-      <c r="W67" s="280"/>
-      <c r="X67" s="215"/>
-      <c r="Y67" s="215"/>
-      <c r="Z67" s="234"/>
+      <c r="W67" s="227"/>
+      <c r="X67" s="164"/>
+      <c r="Y67" s="164"/>
+      <c r="Z67" s="183"/>
       <c r="AA67" s="99"/>
       <c r="AB67" s="58" t="e">
         <f>ROUND((((W67*I67)+(X67*J67)+(Y67*K67)+(Z67*L67)+(AA67*M67))/$I$2),2)*13</f>
@@ -8124,15 +8124,15 @@
     <row r="68" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A68" s="45"/>
       <c r="B68" s="46"/>
-      <c r="C68" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D68" s="206"/>
-      <c r="E68" s="206"/>
-      <c r="F68" s="206"/>
-      <c r="G68" s="207"/>
+      <c r="C68" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D68" s="233"/>
+      <c r="E68" s="233"/>
+      <c r="F68" s="233"/>
+      <c r="G68" s="234"/>
       <c r="H68" s="122"/>
-      <c r="I68" s="273"/>
+      <c r="I68" s="220"/>
       <c r="J68" s="89"/>
       <c r="K68" s="89"/>
       <c r="L68" s="89"/>
@@ -8158,7 +8158,7 @@
       <c r="AC68" s="59"/>
       <c r="AD68" s="56"/>
       <c r="AE68" s="56"/>
-      <c r="AF68" s="208"/>
+      <c r="AF68" s="157"/>
       <c r="AG68" s="100"/>
       <c r="AH68" s="63"/>
       <c r="AI68" s="101"/>
@@ -8185,12 +8185,12 @@
     <row r="69" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A69" s="87"/>
       <c r="B69" s="46"/>
-      <c r="C69" s="276"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="87"/>
       <c r="E69" s="87"/>
-      <c r="F69" s="281"/>
+      <c r="F69" s="228"/>
       <c r="G69" s="87"/>
-      <c r="H69" s="211"/>
+      <c r="H69" s="160"/>
       <c r="I69" s="48"/>
       <c r="J69" s="50"/>
       <c r="K69" s="50"/>
@@ -8206,7 +8206,7 @@
       <c r="P69" s="92"/>
       <c r="Q69" s="93"/>
       <c r="R69" s="93"/>
-      <c r="S69" s="267"/>
+      <c r="S69" s="214"/>
       <c r="T69" s="95"/>
       <c r="U69" s="56">
         <f t="shared" si="12"/>
@@ -8216,10 +8216,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W69" s="214"/>
+      <c r="W69" s="163"/>
       <c r="X69" s="126"/>
-      <c r="Y69" s="257"/>
-      <c r="Z69" s="234"/>
+      <c r="Y69" s="204"/>
+      <c r="Z69" s="183"/>
       <c r="AA69" s="99"/>
       <c r="AB69" s="58" t="e">
         <f t="shared" si="3"/>
@@ -8291,15 +8291,15 @@
     <row r="70" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A70" s="45"/>
       <c r="B70" s="46"/>
-      <c r="C70" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D70" s="206"/>
-      <c r="E70" s="206"/>
-      <c r="F70" s="206"/>
-      <c r="G70" s="207"/>
+      <c r="C70" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D70" s="233"/>
+      <c r="E70" s="233"/>
+      <c r="F70" s="233"/>
+      <c r="G70" s="234"/>
       <c r="H70" s="122"/>
-      <c r="I70" s="273"/>
+      <c r="I70" s="220"/>
       <c r="J70" s="89"/>
       <c r="K70" s="89"/>
       <c r="L70" s="89"/>
@@ -8325,7 +8325,7 @@
       <c r="AC70" s="59"/>
       <c r="AD70" s="56"/>
       <c r="AE70" s="56"/>
-      <c r="AF70" s="208"/>
+      <c r="AF70" s="157"/>
       <c r="AG70" s="100"/>
       <c r="AH70" s="63"/>
       <c r="AI70" s="101"/>
@@ -8352,12 +8352,12 @@
     <row r="71" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A71" s="45"/>
       <c r="B71" s="46"/>
-      <c r="C71" s="276"/>
+      <c r="C71" s="223"/>
       <c r="D71" s="87"/>
       <c r="E71" s="87"/>
       <c r="F71" s="87"/>
       <c r="G71" s="105"/>
-      <c r="H71" s="211"/>
+      <c r="H71" s="160"/>
       <c r="I71" s="48"/>
       <c r="J71" s="50"/>
       <c r="K71" s="50"/>
@@ -8383,9 +8383,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W71" s="250"/>
+      <c r="W71" s="199"/>
       <c r="X71" s="97"/>
-      <c r="Y71" s="247"/>
+      <c r="Y71" s="196"/>
       <c r="Z71" s="57"/>
       <c r="AA71" s="99"/>
       <c r="AB71" s="58" t="e">
@@ -8458,15 +8458,15 @@
     <row r="72" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A72" s="45"/>
       <c r="B72" s="46"/>
-      <c r="C72" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D72" s="206"/>
-      <c r="E72" s="206"/>
-      <c r="F72" s="206"/>
-      <c r="G72" s="207"/>
+      <c r="C72" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D72" s="233"/>
+      <c r="E72" s="233"/>
+      <c r="F72" s="233"/>
+      <c r="G72" s="234"/>
       <c r="H72" s="122"/>
-      <c r="I72" s="273"/>
+      <c r="I72" s="220"/>
       <c r="J72" s="89"/>
       <c r="K72" s="89"/>
       <c r="L72" s="89"/>
@@ -8492,7 +8492,7 @@
       <c r="AC72" s="59"/>
       <c r="AD72" s="56"/>
       <c r="AE72" s="56"/>
-      <c r="AF72" s="208"/>
+      <c r="AF72" s="157"/>
       <c r="AG72" s="100"/>
       <c r="AH72" s="63"/>
       <c r="AI72" s="101"/>
@@ -8519,12 +8519,12 @@
     <row r="73" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A73" s="45"/>
       <c r="B73" s="46"/>
-      <c r="C73" s="276"/>
-      <c r="D73" s="282"/>
-      <c r="E73" s="282"/>
-      <c r="F73" s="282"/>
+      <c r="C73" s="223"/>
+      <c r="D73" s="229"/>
+      <c r="E73" s="229"/>
+      <c r="F73" s="229"/>
       <c r="G73" s="105"/>
-      <c r="H73" s="211"/>
+      <c r="H73" s="160"/>
       <c r="I73" s="48"/>
       <c r="J73" s="50"/>
       <c r="K73" s="50"/>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="P73" s="54"/>
       <c r="Q73" s="55"/>
-      <c r="R73" s="245"/>
+      <c r="R73" s="194"/>
       <c r="S73" s="76"/>
       <c r="T73" s="95"/>
       <c r="U73" s="56">
@@ -8550,10 +8550,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W73" s="214"/>
+      <c r="W73" s="163"/>
       <c r="X73" s="88"/>
-      <c r="Y73" s="250"/>
-      <c r="Z73" s="250"/>
+      <c r="Y73" s="199"/>
+      <c r="Z73" s="199"/>
       <c r="AA73" s="99"/>
       <c r="AB73" s="58" t="e">
         <f t="shared" si="3"/>
@@ -8625,15 +8625,15 @@
     <row r="74" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A74" s="45"/>
       <c r="B74" s="46"/>
-      <c r="C74" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D74" s="206"/>
-      <c r="E74" s="206"/>
-      <c r="F74" s="206"/>
-      <c r="G74" s="207"/>
+      <c r="C74" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D74" s="233"/>
+      <c r="E74" s="233"/>
+      <c r="F74" s="233"/>
+      <c r="G74" s="234"/>
       <c r="H74" s="122"/>
-      <c r="I74" s="273"/>
+      <c r="I74" s="220"/>
       <c r="J74" s="89"/>
       <c r="K74" s="89"/>
       <c r="L74" s="89"/>
@@ -8659,7 +8659,7 @@
       <c r="AC74" s="59"/>
       <c r="AD74" s="56"/>
       <c r="AE74" s="56"/>
-      <c r="AF74" s="208"/>
+      <c r="AF74" s="157"/>
       <c r="AG74" s="100"/>
       <c r="AH74" s="63"/>
       <c r="AI74" s="101"/>
@@ -8691,7 +8691,7 @@
       <c r="E75" s="87"/>
       <c r="F75" s="47"/>
       <c r="G75" s="105"/>
-      <c r="H75" s="211"/>
+      <c r="H75" s="160"/>
       <c r="I75" s="48"/>
       <c r="J75" s="50"/>
       <c r="K75" s="50"/>
@@ -8707,7 +8707,7 @@
       <c r="P75" s="92"/>
       <c r="Q75" s="93"/>
       <c r="R75" s="93"/>
-      <c r="S75" s="267"/>
+      <c r="S75" s="214"/>
       <c r="T75" s="95"/>
       <c r="U75" s="56">
         <f t="shared" si="12"/>
@@ -8792,15 +8792,15 @@
     <row r="76" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A76" s="45"/>
       <c r="B76" s="46"/>
-      <c r="C76" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D76" s="206"/>
-      <c r="E76" s="206"/>
-      <c r="F76" s="206"/>
-      <c r="G76" s="207"/>
+      <c r="C76" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D76" s="233"/>
+      <c r="E76" s="233"/>
+      <c r="F76" s="233"/>
+      <c r="G76" s="234"/>
       <c r="H76" s="122"/>
-      <c r="I76" s="273"/>
+      <c r="I76" s="220"/>
       <c r="J76" s="89"/>
       <c r="K76" s="89"/>
       <c r="L76" s="89"/>
@@ -8826,7 +8826,7 @@
       <c r="AC76" s="59"/>
       <c r="AD76" s="56"/>
       <c r="AE76" s="56"/>
-      <c r="AF76" s="208"/>
+      <c r="AF76" s="157"/>
       <c r="AG76" s="100"/>
       <c r="AH76" s="63"/>
       <c r="AI76" s="101"/>
@@ -8858,7 +8858,7 @@
       <c r="E77" s="87"/>
       <c r="F77" s="47"/>
       <c r="G77" s="105"/>
-      <c r="H77" s="211"/>
+      <c r="H77" s="160"/>
       <c r="I77" s="48"/>
       <c r="J77" s="50"/>
       <c r="K77" s="50"/>
@@ -8874,7 +8874,7 @@
       <c r="P77" s="92"/>
       <c r="Q77" s="93"/>
       <c r="R77" s="93"/>
-      <c r="S77" s="267"/>
+      <c r="S77" s="214"/>
       <c r="T77" s="95"/>
       <c r="U77" s="56">
         <f t="shared" si="12"/>
@@ -8959,15 +8959,15 @@
     <row r="78" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A78" s="45"/>
       <c r="B78" s="46"/>
-      <c r="C78" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D78" s="206"/>
-      <c r="E78" s="206"/>
-      <c r="F78" s="206"/>
-      <c r="G78" s="207"/>
+      <c r="C78" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D78" s="233"/>
+      <c r="E78" s="233"/>
+      <c r="F78" s="233"/>
+      <c r="G78" s="234"/>
       <c r="H78" s="122"/>
-      <c r="I78" s="273"/>
+      <c r="I78" s="220"/>
       <c r="J78" s="89"/>
       <c r="K78" s="89"/>
       <c r="L78" s="89"/>
@@ -8993,7 +8993,7 @@
       <c r="AC78" s="59"/>
       <c r="AD78" s="56"/>
       <c r="AE78" s="56"/>
-      <c r="AF78" s="208"/>
+      <c r="AF78" s="157"/>
       <c r="AG78" s="100"/>
       <c r="AH78" s="63"/>
       <c r="AI78" s="101"/>
@@ -9025,7 +9025,7 @@
       <c r="E79" s="87"/>
       <c r="F79" s="47"/>
       <c r="G79" s="105"/>
-      <c r="H79" s="211"/>
+      <c r="H79" s="160"/>
       <c r="I79" s="48"/>
       <c r="J79" s="50"/>
       <c r="K79" s="50"/>
@@ -9041,7 +9041,7 @@
       <c r="P79" s="92"/>
       <c r="Q79" s="93"/>
       <c r="R79" s="93"/>
-      <c r="S79" s="267"/>
+      <c r="S79" s="214"/>
       <c r="T79" s="95"/>
       <c r="U79" s="56">
         <f t="shared" si="12"/>
@@ -9126,15 +9126,15 @@
     <row r="80" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A80" s="45"/>
       <c r="B80" s="46"/>
-      <c r="C80" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D80" s="206"/>
-      <c r="E80" s="206"/>
-      <c r="F80" s="206"/>
-      <c r="G80" s="207"/>
+      <c r="C80" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D80" s="233"/>
+      <c r="E80" s="233"/>
+      <c r="F80" s="233"/>
+      <c r="G80" s="234"/>
       <c r="H80" s="122"/>
-      <c r="I80" s="273"/>
+      <c r="I80" s="220"/>
       <c r="J80" s="89"/>
       <c r="K80" s="89"/>
       <c r="L80" s="89"/>
@@ -9160,7 +9160,7 @@
       <c r="AC80" s="59"/>
       <c r="AD80" s="56"/>
       <c r="AE80" s="56"/>
-      <c r="AF80" s="208"/>
+      <c r="AF80" s="157"/>
       <c r="AG80" s="100"/>
       <c r="AH80" s="63"/>
       <c r="AI80" s="101"/>
@@ -9192,7 +9192,7 @@
       <c r="E81" s="113"/>
       <c r="F81" s="47"/>
       <c r="G81" s="105"/>
-      <c r="H81" s="211"/>
+      <c r="H81" s="160"/>
       <c r="I81" s="48"/>
       <c r="J81" s="50"/>
       <c r="K81" s="50"/>
@@ -9208,7 +9208,7 @@
       <c r="P81" s="92"/>
       <c r="Q81" s="93"/>
       <c r="R81" s="93"/>
-      <c r="S81" s="267"/>
+      <c r="S81" s="214"/>
       <c r="T81" s="95"/>
       <c r="U81" s="56">
         <f t="shared" ref="U81:U144" si="70">ROUND(((P81*I81)+(Q81*J81)+(R81*K81)+(S81*L81)+(T81*M81))*O81,2)</f>
@@ -9293,15 +9293,15 @@
     <row r="82" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A82" s="45"/>
       <c r="B82" s="46"/>
-      <c r="C82" s="205" t="s">
-        <v>68</v>
-      </c>
-      <c r="D82" s="206"/>
-      <c r="E82" s="206"/>
-      <c r="F82" s="206"/>
-      <c r="G82" s="207"/>
+      <c r="C82" s="232" t="s">
+        <v>67</v>
+      </c>
+      <c r="D82" s="233"/>
+      <c r="E82" s="233"/>
+      <c r="F82" s="233"/>
+      <c r="G82" s="234"/>
       <c r="H82" s="122"/>
-      <c r="I82" s="273"/>
+      <c r="I82" s="220"/>
       <c r="J82" s="89"/>
       <c r="K82" s="89"/>
       <c r="L82" s="89"/>
@@ -9327,7 +9327,7 @@
       <c r="AC82" s="59"/>
       <c r="AD82" s="56"/>
       <c r="AE82" s="56"/>
-      <c r="AF82" s="208"/>
+      <c r="AF82" s="157"/>
       <c r="AG82" s="100"/>
       <c r="AH82" s="63"/>
       <c r="AI82" s="101"/>
@@ -9357,9 +9357,9 @@
       <c r="C83" s="87"/>
       <c r="D83" s="87"/>
       <c r="E83" s="87"/>
-      <c r="F83" s="279"/>
-      <c r="G83" s="283"/>
-      <c r="H83" s="211"/>
+      <c r="F83" s="226"/>
+      <c r="G83" s="230"/>
+      <c r="H83" s="160"/>
       <c r="I83" s="48"/>
       <c r="J83" s="50"/>
       <c r="K83" s="50"/>
@@ -9375,7 +9375,7 @@
       <c r="P83" s="92"/>
       <c r="Q83" s="93"/>
       <c r="R83" s="93"/>
-      <c r="S83" s="267"/>
+      <c r="S83" s="214"/>
       <c r="T83" s="95"/>
       <c r="U83" s="56">
         <f t="shared" si="70"/>
@@ -9460,15 +9460,15 @@
     <row r="84" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A84" s="45"/>
       <c r="B84" s="46"/>
-      <c r="C84" s="205" t="s">
-        <v>68</v>
-      </c>
-      <c r="D84" s="206"/>
-      <c r="E84" s="206"/>
-      <c r="F84" s="206"/>
-      <c r="G84" s="207"/>
+      <c r="C84" s="232" t="s">
+        <v>67</v>
+      </c>
+      <c r="D84" s="233"/>
+      <c r="E84" s="233"/>
+      <c r="F84" s="233"/>
+      <c r="G84" s="234"/>
       <c r="H84" s="122"/>
-      <c r="I84" s="273"/>
+      <c r="I84" s="220"/>
       <c r="J84" s="89"/>
       <c r="K84" s="89"/>
       <c r="L84" s="89"/>
@@ -9494,7 +9494,7 @@
       <c r="AC84" s="59"/>
       <c r="AD84" s="56"/>
       <c r="AE84" s="56"/>
-      <c r="AF84" s="208"/>
+      <c r="AF84" s="157"/>
       <c r="AG84" s="100"/>
       <c r="AH84" s="63"/>
       <c r="AI84" s="101"/>
@@ -9526,7 +9526,7 @@
       <c r="E85" s="114"/>
       <c r="F85" s="115"/>
       <c r="G85" s="116"/>
-      <c r="H85" s="211"/>
+      <c r="H85" s="160"/>
       <c r="I85" s="48"/>
       <c r="J85" s="50"/>
       <c r="K85" s="50"/>
@@ -9542,7 +9542,7 @@
       <c r="P85" s="92"/>
       <c r="Q85" s="93"/>
       <c r="R85" s="93"/>
-      <c r="S85" s="267"/>
+      <c r="S85" s="214"/>
       <c r="T85" s="95"/>
       <c r="U85" s="56">
         <f t="shared" si="70"/>
@@ -9627,15 +9627,15 @@
     <row r="86" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A86" s="45"/>
       <c r="B86" s="46"/>
-      <c r="C86" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D86" s="206"/>
-      <c r="E86" s="206"/>
-      <c r="F86" s="206"/>
-      <c r="G86" s="207"/>
+      <c r="C86" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D86" s="233"/>
+      <c r="E86" s="233"/>
+      <c r="F86" s="233"/>
+      <c r="G86" s="234"/>
       <c r="H86" s="122"/>
-      <c r="I86" s="273"/>
+      <c r="I86" s="220"/>
       <c r="J86" s="89"/>
       <c r="K86" s="89"/>
       <c r="L86" s="89"/>
@@ -9661,7 +9661,7 @@
       <c r="AC86" s="59"/>
       <c r="AD86" s="56"/>
       <c r="AE86" s="56"/>
-      <c r="AF86" s="208"/>
+      <c r="AF86" s="157"/>
       <c r="AG86" s="100"/>
       <c r="AH86" s="63"/>
       <c r="AI86" s="101"/>
@@ -9693,7 +9693,7 @@
       <c r="E87" s="114"/>
       <c r="F87" s="115"/>
       <c r="G87" s="116"/>
-      <c r="H87" s="211"/>
+      <c r="H87" s="160"/>
       <c r="I87" s="48"/>
       <c r="J87" s="50"/>
       <c r="K87" s="50"/>
@@ -9709,7 +9709,7 @@
       <c r="P87" s="92"/>
       <c r="Q87" s="93"/>
       <c r="R87" s="93"/>
-      <c r="S87" s="267"/>
+      <c r="S87" s="214"/>
       <c r="T87" s="95"/>
       <c r="U87" s="56">
         <f t="shared" si="70"/>
@@ -9794,15 +9794,15 @@
     <row r="88" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A88" s="45"/>
       <c r="B88" s="46"/>
-      <c r="C88" s="205" t="s">
-        <v>65</v>
-      </c>
-      <c r="D88" s="206"/>
-      <c r="E88" s="206"/>
-      <c r="F88" s="206"/>
-      <c r="G88" s="207"/>
+      <c r="C88" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D88" s="233"/>
+      <c r="E88" s="233"/>
+      <c r="F88" s="233"/>
+      <c r="G88" s="234"/>
       <c r="H88" s="122"/>
-      <c r="I88" s="273"/>
+      <c r="I88" s="220"/>
       <c r="J88" s="89"/>
       <c r="K88" s="89"/>
       <c r="L88" s="89"/>
@@ -9828,7 +9828,7 @@
       <c r="AC88" s="59"/>
       <c r="AD88" s="56"/>
       <c r="AE88" s="56"/>
-      <c r="AF88" s="208"/>
+      <c r="AF88" s="157"/>
       <c r="AG88" s="100"/>
       <c r="AH88" s="63"/>
       <c r="AI88" s="101"/>
@@ -9860,7 +9860,7 @@
       <c r="E89" s="114"/>
       <c r="F89" s="115"/>
       <c r="G89" s="116"/>
-      <c r="H89" s="211"/>
+      <c r="H89" s="160"/>
       <c r="I89" s="48"/>
       <c r="J89" s="50"/>
       <c r="K89" s="50"/>
@@ -9876,7 +9876,7 @@
       <c r="P89" s="92"/>
       <c r="Q89" s="93"/>
       <c r="R89" s="93"/>
-      <c r="S89" s="267"/>
+      <c r="S89" s="214"/>
       <c r="T89" s="95"/>
       <c r="U89" s="56">
         <f t="shared" si="70"/>
@@ -9966,7 +9966,7 @@
       <c r="E90" s="114"/>
       <c r="F90" s="115"/>
       <c r="G90" s="116"/>
-      <c r="H90" s="211"/>
+      <c r="H90" s="160"/>
       <c r="I90" s="48"/>
       <c r="J90" s="50"/>
       <c r="K90" s="50"/>
@@ -9982,7 +9982,7 @@
       <c r="P90" s="92"/>
       <c r="Q90" s="93"/>
       <c r="R90" s="93"/>
-      <c r="S90" s="267"/>
+      <c r="S90" s="214"/>
       <c r="T90" s="95"/>
       <c r="U90" s="56">
         <f t="shared" si="70"/>
@@ -10072,7 +10072,7 @@
       <c r="E91" s="114"/>
       <c r="F91" s="115"/>
       <c r="G91" s="116"/>
-      <c r="H91" s="211"/>
+      <c r="H91" s="160"/>
       <c r="I91" s="48"/>
       <c r="J91" s="50"/>
       <c r="K91" s="50"/>
@@ -10178,7 +10178,7 @@
       <c r="E92" s="114"/>
       <c r="F92" s="115"/>
       <c r="G92" s="116"/>
-      <c r="H92" s="211"/>
+      <c r="H92" s="160"/>
       <c r="I92" s="48"/>
       <c r="J92" s="50"/>
       <c r="K92" s="50"/>
@@ -10284,7 +10284,7 @@
       <c r="E93" s="114"/>
       <c r="F93" s="115"/>
       <c r="G93" s="116"/>
-      <c r="H93" s="211"/>
+      <c r="H93" s="160"/>
       <c r="I93" s="48"/>
       <c r="J93" s="50"/>
       <c r="K93" s="50"/>
@@ -10390,7 +10390,7 @@
       <c r="E94" s="114"/>
       <c r="F94" s="115"/>
       <c r="G94" s="116"/>
-      <c r="H94" s="211"/>
+      <c r="H94" s="160"/>
       <c r="I94" s="48"/>
       <c r="J94" s="50"/>
       <c r="K94" s="50"/>
@@ -10496,7 +10496,7 @@
       <c r="E95" s="114"/>
       <c r="F95" s="115"/>
       <c r="G95" s="116"/>
-      <c r="H95" s="211"/>
+      <c r="H95" s="160"/>
       <c r="I95" s="48"/>
       <c r="J95" s="50"/>
       <c r="K95" s="50"/>
@@ -10602,7 +10602,7 @@
       <c r="E96" s="114"/>
       <c r="F96" s="115"/>
       <c r="G96" s="116"/>
-      <c r="H96" s="211"/>
+      <c r="H96" s="160"/>
       <c r="I96" s="48"/>
       <c r="J96" s="50"/>
       <c r="K96" s="50"/>
@@ -10708,7 +10708,7 @@
       <c r="E97" s="114"/>
       <c r="F97" s="115"/>
       <c r="G97" s="116"/>
-      <c r="H97" s="211"/>
+      <c r="H97" s="160"/>
       <c r="I97" s="48"/>
       <c r="J97" s="50"/>
       <c r="K97" s="50"/>
@@ -10814,7 +10814,7 @@
       <c r="E98" s="114"/>
       <c r="F98" s="115"/>
       <c r="G98" s="116"/>
-      <c r="H98" s="211"/>
+      <c r="H98" s="160"/>
       <c r="I98" s="48"/>
       <c r="J98" s="50"/>
       <c r="K98" s="50"/>
@@ -10920,7 +10920,7 @@
       <c r="E99" s="114"/>
       <c r="F99" s="115"/>
       <c r="G99" s="116"/>
-      <c r="H99" s="211"/>
+      <c r="H99" s="160"/>
       <c r="I99" s="48"/>
       <c r="J99" s="50"/>
       <c r="K99" s="50"/>
@@ -11026,7 +11026,7 @@
       <c r="E100" s="114"/>
       <c r="F100" s="115"/>
       <c r="G100" s="116"/>
-      <c r="H100" s="284"/>
+      <c r="H100" s="231"/>
       <c r="I100" s="48"/>
       <c r="J100" s="50"/>
       <c r="K100" s="50"/>
@@ -11132,7 +11132,7 @@
       <c r="E101" s="114"/>
       <c r="F101" s="115"/>
       <c r="G101" s="116"/>
-      <c r="H101" s="284"/>
+      <c r="H101" s="231"/>
       <c r="I101" s="48"/>
       <c r="J101" s="50"/>
       <c r="K101" s="50"/>
@@ -11238,7 +11238,7 @@
       <c r="E102" s="114"/>
       <c r="F102" s="115"/>
       <c r="G102" s="116"/>
-      <c r="H102" s="284"/>
+      <c r="H102" s="231"/>
       <c r="I102" s="48"/>
       <c r="J102" s="50"/>
       <c r="K102" s="50"/>
@@ -11344,7 +11344,7 @@
       <c r="E103" s="114"/>
       <c r="F103" s="115"/>
       <c r="G103" s="116"/>
-      <c r="H103" s="284"/>
+      <c r="H103" s="231"/>
       <c r="I103" s="48"/>
       <c r="J103" s="50"/>
       <c r="K103" s="50"/>
@@ -11450,7 +11450,7 @@
       <c r="E104" s="114"/>
       <c r="F104" s="115"/>
       <c r="G104" s="116"/>
-      <c r="H104" s="284"/>
+      <c r="H104" s="231"/>
       <c r="I104" s="48"/>
       <c r="J104" s="50"/>
       <c r="K104" s="50"/>
@@ -11556,7 +11556,7 @@
       <c r="E105" s="114"/>
       <c r="F105" s="115"/>
       <c r="G105" s="116"/>
-      <c r="H105" s="284"/>
+      <c r="H105" s="231"/>
       <c r="I105" s="48"/>
       <c r="J105" s="50"/>
       <c r="K105" s="50"/>
@@ -11662,7 +11662,7 @@
       <c r="E106" s="114"/>
       <c r="F106" s="115"/>
       <c r="G106" s="116"/>
-      <c r="H106" s="284"/>
+      <c r="H106" s="231"/>
       <c r="I106" s="48"/>
       <c r="J106" s="50"/>
       <c r="K106" s="50"/>
@@ -11768,7 +11768,7 @@
       <c r="E107" s="114"/>
       <c r="F107" s="115"/>
       <c r="G107" s="116"/>
-      <c r="H107" s="284"/>
+      <c r="H107" s="231"/>
       <c r="I107" s="48"/>
       <c r="J107" s="50"/>
       <c r="K107" s="50"/>
@@ -11874,7 +11874,7 @@
       <c r="E108" s="114"/>
       <c r="F108" s="115"/>
       <c r="G108" s="116"/>
-      <c r="H108" s="284"/>
+      <c r="H108" s="231"/>
       <c r="I108" s="48"/>
       <c r="J108" s="50"/>
       <c r="K108" s="50"/>
@@ -11980,7 +11980,7 @@
       <c r="E109" s="114"/>
       <c r="F109" s="115"/>
       <c r="G109" s="116"/>
-      <c r="H109" s="284"/>
+      <c r="H109" s="231"/>
       <c r="I109" s="48"/>
       <c r="J109" s="50"/>
       <c r="K109" s="50"/>
@@ -12086,7 +12086,7 @@
       <c r="E110" s="114"/>
       <c r="F110" s="115"/>
       <c r="G110" s="116"/>
-      <c r="H110" s="284"/>
+      <c r="H110" s="231"/>
       <c r="I110" s="48"/>
       <c r="J110" s="50"/>
       <c r="K110" s="50"/>
@@ -12192,7 +12192,7 @@
       <c r="E111" s="114"/>
       <c r="F111" s="115"/>
       <c r="G111" s="116"/>
-      <c r="H111" s="284"/>
+      <c r="H111" s="231"/>
       <c r="I111" s="48"/>
       <c r="J111" s="50"/>
       <c r="K111" s="50"/>
@@ -12298,7 +12298,7 @@
       <c r="E112" s="114"/>
       <c r="F112" s="115"/>
       <c r="G112" s="116"/>
-      <c r="H112" s="284"/>
+      <c r="H112" s="231"/>
       <c r="I112" s="48"/>
       <c r="J112" s="50"/>
       <c r="K112" s="50"/>
@@ -12404,7 +12404,7 @@
       <c r="E113" s="114"/>
       <c r="F113" s="115"/>
       <c r="G113" s="116"/>
-      <c r="H113" s="284"/>
+      <c r="H113" s="231"/>
       <c r="I113" s="48"/>
       <c r="J113" s="50"/>
       <c r="K113" s="50"/>
@@ -12510,7 +12510,7 @@
       <c r="E114" s="114"/>
       <c r="F114" s="114"/>
       <c r="G114" s="116"/>
-      <c r="H114" s="284"/>
+      <c r="H114" s="231"/>
       <c r="I114" s="48"/>
       <c r="J114" s="50"/>
       <c r="K114" s="50"/>
@@ -12616,7 +12616,7 @@
       <c r="E115" s="114"/>
       <c r="F115" s="114"/>
       <c r="G115" s="116"/>
-      <c r="H115" s="284"/>
+      <c r="H115" s="231"/>
       <c r="I115" s="48"/>
       <c r="J115" s="50"/>
       <c r="K115" s="50"/>
@@ -12722,7 +12722,7 @@
       <c r="E116" s="114"/>
       <c r="F116" s="114"/>
       <c r="G116" s="116"/>
-      <c r="H116" s="284"/>
+      <c r="H116" s="231"/>
       <c r="I116" s="48"/>
       <c r="J116" s="50"/>
       <c r="K116" s="50"/>
@@ -12828,7 +12828,7 @@
       <c r="E117" s="114"/>
       <c r="F117" s="114"/>
       <c r="G117" s="116"/>
-      <c r="H117" s="284"/>
+      <c r="H117" s="231"/>
       <c r="I117" s="48"/>
       <c r="J117" s="50"/>
       <c r="K117" s="50"/>
@@ -12934,7 +12934,7 @@
       <c r="E118" s="114"/>
       <c r="F118" s="114"/>
       <c r="G118" s="116"/>
-      <c r="H118" s="284"/>
+      <c r="H118" s="231"/>
       <c r="I118" s="48"/>
       <c r="J118" s="50"/>
       <c r="K118" s="50"/>
@@ -13040,7 +13040,7 @@
       <c r="E119" s="114"/>
       <c r="F119" s="114"/>
       <c r="G119" s="116"/>
-      <c r="H119" s="284"/>
+      <c r="H119" s="231"/>
       <c r="I119" s="48"/>
       <c r="J119" s="50"/>
       <c r="K119" s="50"/>
@@ -13146,7 +13146,7 @@
       <c r="E120" s="114"/>
       <c r="F120" s="114"/>
       <c r="G120" s="116"/>
-      <c r="H120" s="284"/>
+      <c r="H120" s="231"/>
       <c r="I120" s="48"/>
       <c r="J120" s="50"/>
       <c r="K120" s="50"/>
@@ -13252,7 +13252,7 @@
       <c r="E121" s="114"/>
       <c r="F121" s="114"/>
       <c r="G121" s="116"/>
-      <c r="H121" s="284"/>
+      <c r="H121" s="231"/>
       <c r="I121" s="48"/>
       <c r="J121" s="50"/>
       <c r="K121" s="50"/>
@@ -13358,7 +13358,7 @@
       <c r="E122" s="114"/>
       <c r="F122" s="114"/>
       <c r="G122" s="116"/>
-      <c r="H122" s="284"/>
+      <c r="H122" s="231"/>
       <c r="I122" s="48"/>
       <c r="J122" s="50"/>
       <c r="K122" s="50"/>
@@ -13464,7 +13464,7 @@
       <c r="E123" s="114"/>
       <c r="F123" s="114"/>
       <c r="G123" s="116"/>
-      <c r="H123" s="284"/>
+      <c r="H123" s="231"/>
       <c r="I123" s="48"/>
       <c r="J123" s="50"/>
       <c r="K123" s="50"/>
@@ -13570,7 +13570,7 @@
       <c r="E124" s="114"/>
       <c r="F124" s="114"/>
       <c r="G124" s="116"/>
-      <c r="H124" s="284"/>
+      <c r="H124" s="231"/>
       <c r="I124" s="48"/>
       <c r="J124" s="50"/>
       <c r="K124" s="50"/>
@@ -13676,7 +13676,7 @@
       <c r="E125" s="114"/>
       <c r="F125" s="114"/>
       <c r="G125" s="116"/>
-      <c r="H125" s="284"/>
+      <c r="H125" s="231"/>
       <c r="I125" s="48"/>
       <c r="J125" s="50"/>
       <c r="K125" s="50"/>
@@ -13782,7 +13782,7 @@
       <c r="E126" s="114"/>
       <c r="F126" s="114"/>
       <c r="G126" s="116"/>
-      <c r="H126" s="284"/>
+      <c r="H126" s="231"/>
       <c r="I126" s="48"/>
       <c r="J126" s="50"/>
       <c r="K126" s="50"/>
@@ -13888,7 +13888,7 @@
       <c r="E127" s="114"/>
       <c r="F127" s="114"/>
       <c r="G127" s="116"/>
-      <c r="H127" s="284"/>
+      <c r="H127" s="231"/>
       <c r="I127" s="48"/>
       <c r="J127" s="50"/>
       <c r="K127" s="50"/>
@@ -13994,7 +13994,7 @@
       <c r="E128" s="114"/>
       <c r="F128" s="114"/>
       <c r="G128" s="116"/>
-      <c r="H128" s="284"/>
+      <c r="H128" s="231"/>
       <c r="I128" s="48"/>
       <c r="J128" s="50"/>
       <c r="K128" s="50"/>
@@ -14100,7 +14100,7 @@
       <c r="E129" s="114"/>
       <c r="F129" s="114"/>
       <c r="G129" s="116"/>
-      <c r="H129" s="284"/>
+      <c r="H129" s="231"/>
       <c r="I129" s="48"/>
       <c r="J129" s="50"/>
       <c r="K129" s="50"/>
@@ -14206,7 +14206,7 @@
       <c r="E130" s="114"/>
       <c r="F130" s="114"/>
       <c r="G130" s="116"/>
-      <c r="H130" s="284"/>
+      <c r="H130" s="231"/>
       <c r="I130" s="48"/>
       <c r="J130" s="50"/>
       <c r="K130" s="50"/>
@@ -14312,7 +14312,7 @@
       <c r="E131" s="114"/>
       <c r="F131" s="114"/>
       <c r="G131" s="116"/>
-      <c r="H131" s="284"/>
+      <c r="H131" s="231"/>
       <c r="I131" s="48"/>
       <c r="J131" s="50"/>
       <c r="K131" s="50"/>
@@ -14418,7 +14418,7 @@
       <c r="E132" s="114"/>
       <c r="F132" s="114"/>
       <c r="G132" s="116"/>
-      <c r="H132" s="284"/>
+      <c r="H132" s="231"/>
       <c r="I132" s="48"/>
       <c r="J132" s="50"/>
       <c r="K132" s="50"/>
@@ -14524,7 +14524,7 @@
       <c r="E133" s="114"/>
       <c r="F133" s="114"/>
       <c r="G133" s="116"/>
-      <c r="H133" s="284"/>
+      <c r="H133" s="231"/>
       <c r="I133" s="48"/>
       <c r="J133" s="50"/>
       <c r="K133" s="50"/>
@@ -14630,7 +14630,7 @@
       <c r="E134" s="114"/>
       <c r="F134" s="114"/>
       <c r="G134" s="116"/>
-      <c r="H134" s="284"/>
+      <c r="H134" s="231"/>
       <c r="I134" s="48"/>
       <c r="J134" s="50"/>
       <c r="K134" s="50"/>
@@ -14736,7 +14736,7 @@
       <c r="E135" s="114"/>
       <c r="F135" s="114"/>
       <c r="G135" s="116"/>
-      <c r="H135" s="284"/>
+      <c r="H135" s="231"/>
       <c r="I135" s="48"/>
       <c r="J135" s="50"/>
       <c r="K135" s="50"/>
@@ -14842,7 +14842,7 @@
       <c r="E136" s="114"/>
       <c r="F136" s="114"/>
       <c r="G136" s="116"/>
-      <c r="H136" s="284"/>
+      <c r="H136" s="231"/>
       <c r="I136" s="48"/>
       <c r="J136" s="50"/>
       <c r="K136" s="50"/>
@@ -14948,7 +14948,7 @@
       <c r="E137" s="114"/>
       <c r="F137" s="114"/>
       <c r="G137" s="116"/>
-      <c r="H137" s="284"/>
+      <c r="H137" s="231"/>
       <c r="I137" s="48"/>
       <c r="J137" s="50"/>
       <c r="K137" s="50"/>
@@ -15054,7 +15054,7 @@
       <c r="E138" s="114"/>
       <c r="F138" s="114"/>
       <c r="G138" s="116"/>
-      <c r="H138" s="284"/>
+      <c r="H138" s="231"/>
       <c r="I138" s="48"/>
       <c r="J138" s="50"/>
       <c r="K138" s="50"/>
@@ -15160,7 +15160,7 @@
       <c r="E139" s="114"/>
       <c r="F139" s="114"/>
       <c r="G139" s="116"/>
-      <c r="H139" s="284"/>
+      <c r="H139" s="231"/>
       <c r="I139" s="48"/>
       <c r="J139" s="50"/>
       <c r="K139" s="50"/>
@@ -15266,7 +15266,7 @@
       <c r="E140" s="114"/>
       <c r="F140" s="114"/>
       <c r="G140" s="116"/>
-      <c r="H140" s="284"/>
+      <c r="H140" s="231"/>
       <c r="I140" s="48"/>
       <c r="J140" s="50"/>
       <c r="K140" s="50"/>
@@ -15372,7 +15372,7 @@
       <c r="E141" s="114"/>
       <c r="F141" s="114"/>
       <c r="G141" s="116"/>
-      <c r="H141" s="284"/>
+      <c r="H141" s="231"/>
       <c r="I141" s="48"/>
       <c r="J141" s="50"/>
       <c r="K141" s="50"/>
@@ -15478,7 +15478,7 @@
       <c r="E142" s="114"/>
       <c r="F142" s="114"/>
       <c r="G142" s="116"/>
-      <c r="H142" s="284"/>
+      <c r="H142" s="231"/>
       <c r="I142" s="48"/>
       <c r="J142" s="50"/>
       <c r="K142" s="50"/>
@@ -15584,7 +15584,7 @@
       <c r="E143" s="114"/>
       <c r="F143" s="114"/>
       <c r="G143" s="116"/>
-      <c r="H143" s="284"/>
+      <c r="H143" s="231"/>
       <c r="I143" s="48"/>
       <c r="J143" s="50"/>
       <c r="K143" s="50"/>
@@ -15690,7 +15690,7 @@
       <c r="E144" s="114"/>
       <c r="F144" s="114"/>
       <c r="G144" s="116"/>
-      <c r="H144" s="284"/>
+      <c r="H144" s="231"/>
       <c r="I144" s="48"/>
       <c r="J144" s="50"/>
       <c r="K144" s="50"/>
@@ -15784,7 +15784,7 @@
         <v>0</v>
       </c>
       <c r="AZ144" s="74">
-        <f t="shared" ref="AZ144:AZ207" si="84">(AT144*I144)+(AU144*J144)+(AV144*K144)+(AW144*L144)+(AX144*M144)</f>
+        <f t="shared" ref="AZ144" si="84">(AT144*I144)+(AU144*J144)+(AV144*K144)+(AW144*L144)+(AX144*M144)</f>
         <v>0</v>
       </c>
     </row>
@@ -15796,7 +15796,7 @@
       <c r="E145" s="114"/>
       <c r="F145" s="114"/>
       <c r="G145" s="116"/>
-      <c r="H145" s="284"/>
+      <c r="H145" s="231"/>
       <c r="I145" s="48"/>
       <c r="J145" s="50"/>
       <c r="K145" s="50"/>
@@ -15896,42 +15896,33 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="AG1:AJ1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AD2:AL2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="AQ3:AQ4"/>
+    <mergeCell ref="AR3:AR4"/>
+    <mergeCell ref="AS3:AS4"/>
+    <mergeCell ref="AU2:AV2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:U3"/>
+    <mergeCell ref="W3:AE3"/>
+    <mergeCell ref="AF3:AM3"/>
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="AZ3:AZ4"/>
     <mergeCell ref="C6:G6"/>
@@ -15948,33 +15939,42 @@
     <mergeCell ref="AN3:AN4"/>
     <mergeCell ref="AO3:AO4"/>
     <mergeCell ref="AP3:AP4"/>
-    <mergeCell ref="AQ3:AQ4"/>
-    <mergeCell ref="AR3:AR4"/>
-    <mergeCell ref="AS3:AS4"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:U3"/>
-    <mergeCell ref="W3:AE3"/>
-    <mergeCell ref="AF3:AM3"/>
-    <mergeCell ref="AG1:AJ1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AD2:AL2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C86:G86"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/템플릿/LH50억~100억(소방)_템플릿.xlsx
+++ b/템플릿/LH50억~100억(소방)_템플릿.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="68">
   <si>
     <t>참여가능비율</t>
   </si>
@@ -79,10 +79,6 @@
   </si>
   <si>
     <t>날짜</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>경기의무30%, 5개사</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2048,6 +2044,126 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="177" fontId="9" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="4" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -2057,155 +2173,35 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="4" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="21" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2528,15 +2524,15 @@
       <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="275"/>
-      <c r="E1" s="275"/>
+      <c r="D1" s="244"/>
+      <c r="E1" s="244"/>
       <c r="F1" s="4"/>
       <c r="G1" s="5"/>
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="276"/>
-      <c r="J1" s="277"/>
+      <c r="I1" s="245"/>
+      <c r="J1" s="246"/>
       <c r="K1" s="7" t="s">
         <v>5</v>
       </c>
@@ -2551,31 +2547,31 @@
       <c r="T1" s="9"/>
       <c r="U1" s="9"/>
       <c r="V1" s="9"/>
-      <c r="W1" s="278" t="s">
+      <c r="W1" s="247" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="278"/>
-      <c r="Y1" s="279" t="s">
+      <c r="X1" s="247"/>
+      <c r="Y1" s="248" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="280"/>
-      <c r="AA1" s="281" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB1" s="282"/>
+      <c r="Z1" s="249"/>
+      <c r="AA1" s="250" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB1" s="251"/>
       <c r="AC1" s="10"/>
       <c r="AD1" s="10"/>
-      <c r="AE1" s="283" t="s">
+      <c r="AE1" s="252" t="s">
         <v>7</v>
       </c>
-      <c r="AF1" s="284"/>
-      <c r="AG1" s="263">
+      <c r="AF1" s="253"/>
+      <c r="AG1" s="232">
         <f>D1</f>
         <v>0</v>
       </c>
-      <c r="AH1" s="263"/>
-      <c r="AI1" s="263"/>
-      <c r="AJ1" s="263"/>
+      <c r="AH1" s="232"/>
+      <c r="AI1" s="232"/>
+      <c r="AJ1" s="232"/>
       <c r="AK1" s="11" t="s">
         <v>8</v>
       </c>
@@ -2590,63 +2586,61 @@
       <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="264"/>
-      <c r="E2" s="264"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
       <c r="F2" s="15"/>
       <c r="G2" s="16"/>
       <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="265">
+      <c r="I2" s="234">
         <f>D2*3</f>
         <v>0</v>
       </c>
-      <c r="J2" s="266"/>
+      <c r="J2" s="235"/>
       <c r="K2" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="267" t="s">
+      <c r="M2" s="236" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="268"/>
-      <c r="O2" s="268"/>
-      <c r="P2" s="268"/>
-      <c r="Q2" s="19" t="s">
-        <v>13</v>
-      </c>
+      <c r="N2" s="237"/>
+      <c r="O2" s="237"/>
+      <c r="P2" s="237"/>
+      <c r="Q2" s="19"/>
       <c r="R2" s="19"/>
       <c r="S2" s="19"/>
       <c r="T2" s="20"/>
       <c r="U2" s="21"/>
       <c r="V2" s="21"/>
-      <c r="W2" s="269"/>
-      <c r="X2" s="269"/>
-      <c r="Y2" s="270">
+      <c r="W2" s="238"/>
+      <c r="X2" s="238"/>
+      <c r="Y2" s="239">
         <f>I1</f>
         <v>0</v>
       </c>
-      <c r="Z2" s="271"/>
-      <c r="AA2" s="272" t="e">
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="241" t="e">
         <f>TRUNC(W2/Y2,4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB2" s="273"/>
+      <c r="AB2" s="242"/>
       <c r="AC2" s="22"/>
-      <c r="AD2" s="274"/>
-      <c r="AE2" s="274"/>
-      <c r="AF2" s="274"/>
-      <c r="AG2" s="274"/>
-      <c r="AH2" s="274"/>
-      <c r="AI2" s="274"/>
-      <c r="AJ2" s="274"/>
-      <c r="AK2" s="274"/>
-      <c r="AL2" s="274"/>
+      <c r="AD2" s="243"/>
+      <c r="AE2" s="243"/>
+      <c r="AF2" s="243"/>
+      <c r="AG2" s="243"/>
+      <c r="AH2" s="243"/>
+      <c r="AI2" s="243"/>
+      <c r="AJ2" s="243"/>
+      <c r="AK2" s="243"/>
+      <c r="AL2" s="243"/>
       <c r="AM2" s="133"/>
       <c r="AN2" s="24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO2" s="25"/>
       <c r="AP2" s="24"/>
@@ -2654,232 +2648,232 @@
       <c r="AR2" s="24"/>
       <c r="AS2" s="1"/>
       <c r="AT2" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="AU2" s="249">
+        <v>14</v>
+      </c>
+      <c r="AU2" s="258">
         <f>AG1</f>
         <v>0</v>
       </c>
-      <c r="AV2" s="250"/>
+      <c r="AV2" s="259"/>
       <c r="AY2" s="27"/>
     </row>
     <row r="3" spans="1:52" s="28" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="251" t="s">
+      <c r="A3" s="260" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="262" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="253" t="s">
+      <c r="C3" s="264" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="255" t="s">
+      <c r="D3" s="265"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="265"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266"/>
+      <c r="I3" s="264" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="256"/>
-      <c r="H3" s="257"/>
-      <c r="I3" s="255" t="s">
+      <c r="J3" s="265"/>
+      <c r="K3" s="265"/>
+      <c r="L3" s="265"/>
+      <c r="M3" s="266"/>
+      <c r="N3" s="267" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
-      <c r="M3" s="257"/>
-      <c r="N3" s="258" t="s">
+      <c r="O3" s="269" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="260" t="s">
+      <c r="P3" s="264" t="s">
         <v>21</v>
       </c>
-      <c r="P3" s="255" t="s">
+      <c r="Q3" s="265"/>
+      <c r="R3" s="271"/>
+      <c r="S3" s="271"/>
+      <c r="T3" s="265"/>
+      <c r="U3" s="266"/>
+      <c r="V3" s="132"/>
+      <c r="W3" s="264" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="256"/>
-      <c r="R3" s="262"/>
-      <c r="S3" s="262"/>
-      <c r="T3" s="256"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="132"/>
-      <c r="W3" s="255" t="s">
+      <c r="X3" s="265"/>
+      <c r="Y3" s="265"/>
+      <c r="Z3" s="265"/>
+      <c r="AA3" s="265"/>
+      <c r="AB3" s="265"/>
+      <c r="AC3" s="265"/>
+      <c r="AD3" s="265"/>
+      <c r="AE3" s="266"/>
+      <c r="AF3" s="264"/>
+      <c r="AG3" s="265"/>
+      <c r="AH3" s="265"/>
+      <c r="AI3" s="265"/>
+      <c r="AJ3" s="265"/>
+      <c r="AK3" s="265"/>
+      <c r="AL3" s="265"/>
+      <c r="AM3" s="266"/>
+      <c r="AN3" s="279" t="s">
         <v>23</v>
       </c>
-      <c r="X3" s="256"/>
-      <c r="Y3" s="256"/>
-      <c r="Z3" s="256"/>
-      <c r="AA3" s="256"/>
-      <c r="AB3" s="256"/>
-      <c r="AC3" s="256"/>
-      <c r="AD3" s="256"/>
-      <c r="AE3" s="257"/>
-      <c r="AF3" s="255"/>
-      <c r="AG3" s="256"/>
-      <c r="AH3" s="256"/>
-      <c r="AI3" s="256"/>
-      <c r="AJ3" s="256"/>
-      <c r="AK3" s="256"/>
-      <c r="AL3" s="256"/>
-      <c r="AM3" s="257"/>
-      <c r="AN3" s="242" t="s">
+      <c r="AO3" s="275" t="s">
         <v>24</v>
       </c>
-      <c r="AO3" s="238" t="s">
+      <c r="AP3" s="281" t="s">
         <v>25</v>
       </c>
-      <c r="AP3" s="244" t="s">
+      <c r="AQ3" s="254" t="s">
         <v>26</v>
       </c>
-      <c r="AQ3" s="246" t="s">
+      <c r="AR3" s="256" t="s">
         <v>27</v>
       </c>
-      <c r="AR3" s="248" t="s">
+      <c r="AS3" s="257" t="s">
         <v>28</v>
       </c>
-      <c r="AS3" s="237" t="s">
+      <c r="AT3" s="275" t="s">
         <v>29</v>
       </c>
-      <c r="AT3" s="238" t="s">
+      <c r="AU3" s="257" t="s">
         <v>30</v>
       </c>
-      <c r="AU3" s="237" t="s">
+      <c r="AV3" s="257" t="s">
         <v>31</v>
       </c>
-      <c r="AV3" s="237" t="s">
+      <c r="AW3" s="257" t="s">
         <v>32</v>
       </c>
-      <c r="AW3" s="237" t="s">
+      <c r="AX3" s="277" t="s">
         <v>33</v>
       </c>
-      <c r="AX3" s="240" t="s">
+      <c r="AY3" s="257" t="s">
         <v>34</v>
       </c>
-      <c r="AY3" s="237" t="s">
+      <c r="AZ3" s="257" t="s">
         <v>35</v>
-      </c>
-      <c r="AZ3" s="237" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:52" s="28" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="252"/>
-      <c r="B4" s="254"/>
+      <c r="A4" s="261"/>
+      <c r="B4" s="263"/>
       <c r="C4" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="E4" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="F4" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="132" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="M4" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="132" t="s">
+      <c r="N4" s="268"/>
+      <c r="O4" s="270"/>
+      <c r="P4" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="Q4" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="U4" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="V4" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="W4" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="X4" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="Y4" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="L4" s="30" t="s">
+      <c r="Z4" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="35" t="s">
+      <c r="AA4" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="N4" s="259"/>
-      <c r="O4" s="261"/>
-      <c r="P4" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q4" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="R4" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="S4" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="T4" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="U4" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="V4" s="37" t="s">
+      <c r="AB4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="W4" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y4" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z4" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA4" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB4" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="40" t="s">
+      <c r="AD4" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="AD4" s="41" t="s">
+      <c r="AE4" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="AE4" s="41" t="s">
+      <c r="AF4" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="AF4" s="42" t="s">
+      <c r="AG4" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="AG4" s="42" t="s">
+      <c r="AH4" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="AH4" s="43" t="s">
+      <c r="AI4" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="AI4" s="43" t="s">
+      <c r="AJ4" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="AJ4" s="43" t="s">
+      <c r="AK4" s="44" t="s">
         <v>60</v>
-      </c>
-      <c r="AK4" s="44" t="s">
-        <v>61</v>
       </c>
       <c r="AL4" s="44"/>
       <c r="AM4" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN4" s="243"/>
-      <c r="AO4" s="239"/>
-      <c r="AP4" s="245"/>
-      <c r="AQ4" s="247"/>
-      <c r="AR4" s="248"/>
-      <c r="AS4" s="237"/>
-      <c r="AT4" s="239"/>
-      <c r="AU4" s="237"/>
-      <c r="AV4" s="237"/>
-      <c r="AW4" s="237"/>
-      <c r="AX4" s="241"/>
-      <c r="AY4" s="237"/>
-      <c r="AZ4" s="237"/>
+        <v>61</v>
+      </c>
+      <c r="AN4" s="280"/>
+      <c r="AO4" s="276"/>
+      <c r="AP4" s="282"/>
+      <c r="AQ4" s="255"/>
+      <c r="AR4" s="256"/>
+      <c r="AS4" s="257"/>
+      <c r="AT4" s="276"/>
+      <c r="AU4" s="257"/>
+      <c r="AV4" s="257"/>
+      <c r="AW4" s="257"/>
+      <c r="AX4" s="278"/>
+      <c r="AY4" s="257"/>
+      <c r="AZ4" s="257"/>
     </row>
     <row r="5" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="45"/>
@@ -2928,9 +2922,7 @@
         <f>IF(AB5&gt;=13,13,AB5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD5" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD5" s="60"/>
       <c r="AE5" s="56" t="e">
         <f>IF((AC5+AD5)&gt;=15,15,(AC5+AD5))</f>
         <v>#DIV/0!</v>
@@ -2990,13 +2982,13 @@
     <row r="6" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="45"/>
       <c r="B6" s="46"/>
-      <c r="C6" s="232" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="233"/>
-      <c r="E6" s="233"/>
-      <c r="F6" s="233"/>
-      <c r="G6" s="234"/>
+      <c r="C6" s="272" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="273"/>
+      <c r="E6" s="273"/>
+      <c r="F6" s="273"/>
+      <c r="G6" s="274"/>
       <c r="H6" s="122"/>
       <c r="I6" s="89"/>
       <c r="J6" s="130"/>
@@ -3095,9 +3087,7 @@
         <f t="shared" ref="AC7:AC79" si="4">IF(AB7&gt;=13,13,AB7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD7" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD7" s="60"/>
       <c r="AE7" s="56" t="e">
         <f t="shared" ref="AE7:AE79" si="5">IF((AC7+AD7)&gt;=15,15,(AC7+AD7))</f>
         <v>#DIV/0!</v>
@@ -3154,13 +3144,13 @@
     <row r="8" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="45"/>
       <c r="B8" s="46"/>
-      <c r="C8" s="232" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="233"/>
-      <c r="E8" s="233"/>
-      <c r="F8" s="233"/>
-      <c r="G8" s="234"/>
+      <c r="C8" s="272" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="273"/>
+      <c r="E8" s="273"/>
+      <c r="F8" s="273"/>
+      <c r="G8" s="274"/>
       <c r="H8" s="122"/>
       <c r="I8" s="89"/>
       <c r="J8" s="130"/>
@@ -3259,9 +3249,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD9" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD9" s="60"/>
       <c r="AE9" s="79" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -3320,13 +3308,13 @@
     <row r="10" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45"/>
       <c r="B10" s="46"/>
-      <c r="C10" s="232" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="233"/>
-      <c r="E10" s="233"/>
-      <c r="F10" s="233"/>
-      <c r="G10" s="234"/>
+      <c r="C10" s="272" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="273"/>
+      <c r="E10" s="273"/>
+      <c r="F10" s="273"/>
+      <c r="G10" s="274"/>
       <c r="H10" s="122"/>
       <c r="I10" s="89"/>
       <c r="J10" s="130"/>
@@ -3425,9 +3413,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD11" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD11" s="60"/>
       <c r="AE11" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -3486,13 +3472,13 @@
     <row r="12" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45"/>
       <c r="B12" s="46"/>
-      <c r="C12" s="232" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="233"/>
-      <c r="E12" s="233"/>
-      <c r="F12" s="233"/>
-      <c r="G12" s="234"/>
+      <c r="C12" s="272" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="273"/>
+      <c r="E12" s="273"/>
+      <c r="F12" s="273"/>
+      <c r="G12" s="274"/>
       <c r="H12" s="122"/>
       <c r="I12" s="130"/>
       <c r="J12" s="130"/>
@@ -3591,9 +3577,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD13" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD13" s="60"/>
       <c r="AE13" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -3649,13 +3633,13 @@
     <row r="14" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="45"/>
       <c r="B14" s="46"/>
-      <c r="C14" s="232" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="233"/>
-      <c r="E14" s="233"/>
-      <c r="F14" s="233"/>
-      <c r="G14" s="234"/>
+      <c r="C14" s="272" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="273"/>
+      <c r="E14" s="273"/>
+      <c r="F14" s="273"/>
+      <c r="G14" s="274"/>
       <c r="H14" s="122"/>
       <c r="I14" s="89"/>
       <c r="J14" s="130"/>
@@ -3754,9 +3738,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD15" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD15" s="60"/>
       <c r="AE15" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -3816,13 +3798,13 @@
     <row r="16" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="45"/>
       <c r="B16" s="46"/>
-      <c r="C16" s="232" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="233"/>
-      <c r="E16" s="233"/>
-      <c r="F16" s="233"/>
-      <c r="G16" s="235"/>
+      <c r="C16" s="272" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="273"/>
+      <c r="E16" s="273"/>
+      <c r="F16" s="273"/>
+      <c r="G16" s="283"/>
       <c r="H16" s="122"/>
       <c r="I16" s="89"/>
       <c r="J16" s="89"/>
@@ -3921,9 +3903,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD17" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD17" s="60"/>
       <c r="AE17" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -3982,13 +3962,13 @@
     <row r="18" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="45"/>
       <c r="B18" s="46"/>
-      <c r="C18" s="232" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="235"/>
+      <c r="C18" s="272" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="273"/>
+      <c r="E18" s="273"/>
+      <c r="F18" s="273"/>
+      <c r="G18" s="283"/>
       <c r="H18" s="122"/>
       <c r="I18" s="89"/>
       <c r="J18" s="89"/>
@@ -4087,9 +4067,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD19" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD19" s="60"/>
       <c r="AE19" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -4147,13 +4125,13 @@
     <row r="20" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="45"/>
       <c r="B20" s="46"/>
-      <c r="C20" s="232" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="233"/>
-      <c r="E20" s="233"/>
-      <c r="F20" s="233"/>
-      <c r="G20" s="235"/>
+      <c r="C20" s="272" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="273"/>
+      <c r="E20" s="273"/>
+      <c r="F20" s="273"/>
+      <c r="G20" s="283"/>
       <c r="H20" s="122"/>
       <c r="I20" s="89"/>
       <c r="J20" s="89"/>
@@ -4252,9 +4230,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD21" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD21" s="60"/>
       <c r="AE21" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -4312,13 +4288,13 @@
     <row r="22" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="45"/>
       <c r="B22" s="46"/>
-      <c r="C22" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="233"/>
-      <c r="E22" s="233"/>
-      <c r="F22" s="233"/>
-      <c r="G22" s="236"/>
+      <c r="C22" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="273"/>
+      <c r="E22" s="273"/>
+      <c r="F22" s="273"/>
+      <c r="G22" s="284"/>
       <c r="H22" s="122"/>
       <c r="I22" s="130"/>
       <c r="J22" s="130"/>
@@ -4417,9 +4393,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD23" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD23" s="60"/>
       <c r="AE23" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -4477,13 +4451,13 @@
     <row r="24" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A24" s="45"/>
       <c r="B24" s="46"/>
-      <c r="C24" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="233"/>
-      <c r="E24" s="233"/>
-      <c r="F24" s="233"/>
-      <c r="G24" s="234"/>
+      <c r="C24" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="273"/>
+      <c r="E24" s="273"/>
+      <c r="F24" s="273"/>
+      <c r="G24" s="274"/>
       <c r="H24" s="122"/>
       <c r="I24" s="130"/>
       <c r="J24" s="89"/>
@@ -4582,9 +4556,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD25" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD25" s="60"/>
       <c r="AE25" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -4642,13 +4614,13 @@
     <row r="26" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="45"/>
       <c r="B26" s="46"/>
-      <c r="C26" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="233"/>
-      <c r="E26" s="233"/>
-      <c r="F26" s="233"/>
-      <c r="G26" s="234"/>
+      <c r="C26" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="273"/>
+      <c r="E26" s="273"/>
+      <c r="F26" s="273"/>
+      <c r="G26" s="274"/>
       <c r="H26" s="122"/>
       <c r="I26" s="89"/>
       <c r="J26" s="89"/>
@@ -4747,9 +4719,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD27" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD27" s="60"/>
       <c r="AE27" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -4807,13 +4777,13 @@
     <row r="28" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="45"/>
       <c r="B28" s="46"/>
-      <c r="C28" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="233"/>
-      <c r="E28" s="233"/>
-      <c r="F28" s="233"/>
-      <c r="G28" s="234"/>
+      <c r="C28" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="273"/>
+      <c r="E28" s="273"/>
+      <c r="F28" s="273"/>
+      <c r="G28" s="274"/>
       <c r="H28" s="122"/>
       <c r="I28" s="130"/>
       <c r="J28" s="89"/>
@@ -4912,9 +4882,7 @@
         <f t="shared" ref="AC29" si="17">IF(AB29&gt;=13,13,AB29)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD29" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD29" s="60"/>
       <c r="AE29" s="56" t="e">
         <f t="shared" ref="AE29" si="18">IF((AC29+AD29)&gt;=15,15,(AC29+AD29))</f>
         <v>#DIV/0!</v>
@@ -4974,13 +4942,13 @@
     <row r="30" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A30" s="45"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D30" s="233"/>
-      <c r="E30" s="233"/>
-      <c r="F30" s="233"/>
-      <c r="G30" s="234"/>
+      <c r="C30" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="273"/>
+      <c r="E30" s="273"/>
+      <c r="F30" s="273"/>
+      <c r="G30" s="274"/>
       <c r="H30" s="122"/>
       <c r="I30" s="130"/>
       <c r="J30" s="89"/>
@@ -5079,9 +5047,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD31" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD31" s="60"/>
       <c r="AE31" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -5139,13 +5105,13 @@
     <row r="32" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="45"/>
       <c r="B32" s="46"/>
-      <c r="C32" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D32" s="233"/>
-      <c r="E32" s="233"/>
-      <c r="F32" s="233"/>
-      <c r="G32" s="234"/>
+      <c r="C32" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="273"/>
+      <c r="E32" s="273"/>
+      <c r="F32" s="273"/>
+      <c r="G32" s="274"/>
       <c r="H32" s="122"/>
       <c r="I32" s="130"/>
       <c r="J32" s="130"/>
@@ -5244,9 +5210,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD33" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD33" s="60"/>
       <c r="AE33" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -5304,13 +5268,13 @@
     <row r="34" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="45"/>
       <c r="B34" s="46"/>
-      <c r="C34" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="233"/>
-      <c r="E34" s="233"/>
-      <c r="F34" s="233"/>
-      <c r="G34" s="234"/>
+      <c r="C34" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="273"/>
+      <c r="E34" s="273"/>
+      <c r="F34" s="273"/>
+      <c r="G34" s="274"/>
       <c r="H34" s="122"/>
       <c r="I34" s="130"/>
       <c r="J34" s="130"/>
@@ -5409,9 +5373,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD35" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD35" s="60"/>
       <c r="AE35" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -5469,13 +5431,13 @@
     <row r="36" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="45"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" s="233"/>
-      <c r="E36" s="233"/>
-      <c r="F36" s="233"/>
-      <c r="G36" s="234"/>
+      <c r="C36" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="273"/>
+      <c r="E36" s="273"/>
+      <c r="F36" s="273"/>
+      <c r="G36" s="274"/>
       <c r="H36" s="122"/>
       <c r="I36" s="130"/>
       <c r="J36" s="89"/>
@@ -5536,7 +5498,7 @@
       <c r="F37" s="136"/>
       <c r="G37" s="201"/>
       <c r="H37" s="160" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I37" s="195"/>
       <c r="J37" s="129"/>
@@ -5576,9 +5538,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD37" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD37" s="60"/>
       <c r="AE37" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -5636,13 +5596,13 @@
     <row r="38" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A38" s="45"/>
       <c r="B38" s="46"/>
-      <c r="C38" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" s="233"/>
-      <c r="E38" s="233"/>
-      <c r="F38" s="233"/>
-      <c r="G38" s="234"/>
+      <c r="C38" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" s="273"/>
+      <c r="E38" s="273"/>
+      <c r="F38" s="273"/>
+      <c r="G38" s="274"/>
       <c r="H38" s="122"/>
       <c r="I38" s="130"/>
       <c r="J38" s="89"/>
@@ -5741,9 +5701,7 @@
         <f t="shared" ref="AC39" si="29">IF(AB39&gt;=13,13,AB39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD39" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD39" s="60"/>
       <c r="AE39" s="56" t="e">
         <f t="shared" ref="AE39" si="30">IF((AC39+AD39)&gt;=15,15,(AC39+AD39))</f>
         <v>#DIV/0!</v>
@@ -5801,13 +5759,13 @@
     <row r="40" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="45"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D40" s="233"/>
-      <c r="E40" s="233"/>
-      <c r="F40" s="233"/>
-      <c r="G40" s="234"/>
+      <c r="C40" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="273"/>
+      <c r="E40" s="273"/>
+      <c r="F40" s="273"/>
+      <c r="G40" s="274"/>
       <c r="H40" s="122"/>
       <c r="I40" s="130"/>
       <c r="J40" s="130"/>
@@ -5866,7 +5824,7 @@
       <c r="D41" s="200"/>
       <c r="E41" s="115"/>
       <c r="F41" s="115" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G41" s="170"/>
       <c r="H41" s="160"/>
@@ -5908,9 +5866,7 @@
         <f t="shared" ref="AC41" si="40">IF(AB41&gt;=13,13,AB41)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD41" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD41" s="60"/>
       <c r="AE41" s="56" t="e">
         <f t="shared" ref="AE41" si="41">IF((AC41+AD41)&gt;=15,15,(AC41+AD41))</f>
         <v>#DIV/0!</v>
@@ -5970,13 +5926,13 @@
     <row r="42" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="45"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" s="233"/>
-      <c r="E42" s="233"/>
-      <c r="F42" s="233"/>
-      <c r="G42" s="234"/>
+      <c r="C42" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="273"/>
+      <c r="E42" s="273"/>
+      <c r="F42" s="273"/>
+      <c r="G42" s="274"/>
       <c r="H42" s="122"/>
       <c r="I42" s="89"/>
       <c r="J42" s="130"/>
@@ -6075,9 +6031,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD43" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD43" s="60"/>
       <c r="AE43" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -6139,13 +6093,13 @@
     <row r="44" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A44" s="45"/>
       <c r="B44" s="46"/>
-      <c r="C44" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" s="233"/>
-      <c r="E44" s="233"/>
-      <c r="F44" s="233"/>
-      <c r="G44" s="234"/>
+      <c r="C44" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="273"/>
+      <c r="E44" s="273"/>
+      <c r="F44" s="273"/>
+      <c r="G44" s="274"/>
       <c r="H44" s="122"/>
       <c r="I44" s="130"/>
       <c r="J44" s="130"/>
@@ -6244,9 +6198,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD45" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD45" s="60"/>
       <c r="AE45" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -6305,13 +6257,13 @@
     <row r="46" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="45"/>
       <c r="B46" s="87"/>
-      <c r="C46" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D46" s="233"/>
-      <c r="E46" s="233"/>
-      <c r="F46" s="233"/>
-      <c r="G46" s="234"/>
+      <c r="C46" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" s="273"/>
+      <c r="E46" s="273"/>
+      <c r="F46" s="273"/>
+      <c r="G46" s="274"/>
       <c r="H46" s="122"/>
       <c r="I46" s="89"/>
       <c r="J46" s="130"/>
@@ -6410,9 +6362,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD47" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD47" s="60"/>
       <c r="AE47" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -6471,13 +6421,13 @@
     <row r="48" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A48" s="45"/>
       <c r="B48" s="46"/>
-      <c r="C48" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" s="233"/>
-      <c r="E48" s="233"/>
-      <c r="F48" s="233"/>
-      <c r="G48" s="234"/>
+      <c r="C48" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="274"/>
       <c r="H48" s="122"/>
       <c r="I48" s="89"/>
       <c r="J48" s="130"/>
@@ -6576,9 +6526,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD49" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD49" s="60"/>
       <c r="AE49" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -6636,13 +6584,13 @@
     <row r="50" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A50" s="45"/>
       <c r="B50" s="46"/>
-      <c r="C50" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D50" s="233"/>
-      <c r="E50" s="233"/>
-      <c r="F50" s="233"/>
-      <c r="G50" s="234"/>
+      <c r="C50" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50" s="273"/>
+      <c r="E50" s="273"/>
+      <c r="F50" s="273"/>
+      <c r="G50" s="274"/>
       <c r="H50" s="122"/>
       <c r="I50" s="89"/>
       <c r="J50" s="130"/>
@@ -6741,9 +6689,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD51" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD51" s="60"/>
       <c r="AE51" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -6800,13 +6746,13 @@
     <row r="52" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A52" s="45"/>
       <c r="B52" s="46"/>
-      <c r="C52" s="232" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="234"/>
+      <c r="C52" s="272" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" s="273"/>
+      <c r="E52" s="273"/>
+      <c r="F52" s="273"/>
+      <c r="G52" s="274"/>
       <c r="H52" s="122"/>
       <c r="I52" s="89"/>
       <c r="J52" s="130"/>
@@ -6905,9 +6851,7 @@
         <f t="shared" ref="AC53" si="54">IF(AB53&gt;=13,13,AB53)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD53" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD53" s="60"/>
       <c r="AE53" s="56" t="e">
         <f t="shared" ref="AE53" si="55">IF((AC53+AD53)&gt;=15,15,(AC53+AD53))</f>
         <v>#DIV/0!</v>
@@ -6965,13 +6909,13 @@
     <row r="54" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A54" s="45"/>
       <c r="B54" s="46"/>
-      <c r="C54" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D54" s="233"/>
-      <c r="E54" s="233"/>
-      <c r="F54" s="233"/>
-      <c r="G54" s="234"/>
+      <c r="C54" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" s="273"/>
+      <c r="E54" s="273"/>
+      <c r="F54" s="273"/>
+      <c r="G54" s="274"/>
       <c r="H54" s="122"/>
       <c r="I54" s="220"/>
       <c r="J54" s="89"/>
@@ -7070,9 +7014,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD55" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD55" s="60"/>
       <c r="AE55" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -7130,13 +7072,13 @@
     <row r="56" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A56" s="45"/>
       <c r="B56" s="46"/>
-      <c r="C56" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D56" s="233"/>
-      <c r="E56" s="233"/>
-      <c r="F56" s="233"/>
-      <c r="G56" s="234"/>
+      <c r="C56" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" s="273"/>
+      <c r="E56" s="273"/>
+      <c r="F56" s="273"/>
+      <c r="G56" s="274"/>
       <c r="H56" s="122"/>
       <c r="I56" s="220"/>
       <c r="J56" s="89"/>
@@ -7235,9 +7177,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD57" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD57" s="60"/>
       <c r="AE57" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -7293,13 +7233,13 @@
     <row r="58" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A58" s="45"/>
       <c r="B58" s="46"/>
-      <c r="C58" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D58" s="233"/>
-      <c r="E58" s="233"/>
-      <c r="F58" s="233"/>
-      <c r="G58" s="234"/>
+      <c r="C58" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58" s="273"/>
+      <c r="E58" s="273"/>
+      <c r="F58" s="273"/>
+      <c r="G58" s="274"/>
       <c r="H58" s="122"/>
       <c r="I58" s="220"/>
       <c r="J58" s="89"/>
@@ -7398,9 +7338,7 @@
         <f>IF(AB59&gt;=13,13,AB59)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD59" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD59" s="60"/>
       <c r="AE59" s="56" t="e">
         <f>IF((AC59+AD59)&gt;=15,15,(AC59+AD59))</f>
         <v>#DIV/0!</v>
@@ -7457,13 +7395,13 @@
     <row r="60" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A60" s="45"/>
       <c r="B60" s="46"/>
-      <c r="C60" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D60" s="233"/>
-      <c r="E60" s="233"/>
-      <c r="F60" s="233"/>
-      <c r="G60" s="234"/>
+      <c r="C60" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D60" s="273"/>
+      <c r="E60" s="273"/>
+      <c r="F60" s="273"/>
+      <c r="G60" s="274"/>
       <c r="H60" s="122"/>
       <c r="I60" s="220"/>
       <c r="J60" s="89"/>
@@ -7562,9 +7500,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD61" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD61" s="60"/>
       <c r="AE61" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -7623,13 +7559,13 @@
     <row r="62" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A62" s="45"/>
       <c r="B62" s="46"/>
-      <c r="C62" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D62" s="233"/>
-      <c r="E62" s="233"/>
-      <c r="F62" s="233"/>
-      <c r="G62" s="234"/>
+      <c r="C62" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D62" s="273"/>
+      <c r="E62" s="273"/>
+      <c r="F62" s="273"/>
+      <c r="G62" s="274"/>
       <c r="H62" s="122"/>
       <c r="I62" s="220"/>
       <c r="J62" s="89"/>
@@ -7728,9 +7664,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD63" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD63" s="60"/>
       <c r="AE63" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -7790,13 +7724,13 @@
     <row r="64" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A64" s="45"/>
       <c r="B64" s="46"/>
-      <c r="C64" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D64" s="233"/>
-      <c r="E64" s="233"/>
-      <c r="F64" s="233"/>
-      <c r="G64" s="234"/>
+      <c r="C64" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D64" s="273"/>
+      <c r="E64" s="273"/>
+      <c r="F64" s="273"/>
+      <c r="G64" s="274"/>
       <c r="H64" s="122"/>
       <c r="I64" s="220"/>
       <c r="J64" s="89"/>
@@ -7895,9 +7829,7 @@
         <f>IF(AB65&gt;=13,13,AB65)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD65" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD65" s="109"/>
       <c r="AE65" s="56" t="e">
         <f>IF((AC65+AD65)&gt;=15,15,(AC65+AD65))</f>
         <v>#DIV/0!</v>
@@ -7957,13 +7889,13 @@
     <row r="66" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A66" s="45"/>
       <c r="B66" s="46"/>
-      <c r="C66" s="232" t="s">
-        <v>63</v>
-      </c>
-      <c r="D66" s="233"/>
-      <c r="E66" s="233"/>
-      <c r="F66" s="233"/>
-      <c r="G66" s="234"/>
+      <c r="C66" s="272" t="s">
+        <v>62</v>
+      </c>
+      <c r="D66" s="273"/>
+      <c r="E66" s="273"/>
+      <c r="F66" s="273"/>
+      <c r="G66" s="274"/>
       <c r="H66" s="122"/>
       <c r="I66" s="220"/>
       <c r="J66" s="89"/>
@@ -8062,9 +7994,7 @@
         <f>IF(AB67&gt;=13,13,AB67)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD67" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD67" s="60"/>
       <c r="AE67" s="56" t="e">
         <f>IF((AC67+AD67)&gt;=15,15,(AC67+AD67))</f>
         <v>#DIV/0!</v>
@@ -8124,13 +8054,13 @@
     <row r="68" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A68" s="45"/>
       <c r="B68" s="46"/>
-      <c r="C68" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D68" s="233"/>
-      <c r="E68" s="233"/>
-      <c r="F68" s="233"/>
-      <c r="G68" s="234"/>
+      <c r="C68" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D68" s="273"/>
+      <c r="E68" s="273"/>
+      <c r="F68" s="273"/>
+      <c r="G68" s="274"/>
       <c r="H68" s="122"/>
       <c r="I68" s="220"/>
       <c r="J68" s="89"/>
@@ -8229,9 +8159,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD69" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD69" s="109"/>
       <c r="AE69" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -8291,13 +8219,13 @@
     <row r="70" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A70" s="45"/>
       <c r="B70" s="46"/>
-      <c r="C70" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D70" s="233"/>
-      <c r="E70" s="233"/>
-      <c r="F70" s="233"/>
-      <c r="G70" s="234"/>
+      <c r="C70" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D70" s="273"/>
+      <c r="E70" s="273"/>
+      <c r="F70" s="273"/>
+      <c r="G70" s="274"/>
       <c r="H70" s="122"/>
       <c r="I70" s="220"/>
       <c r="J70" s="89"/>
@@ -8396,9 +8324,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD71" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD71" s="60"/>
       <c r="AE71" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -8458,13 +8384,13 @@
     <row r="72" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A72" s="45"/>
       <c r="B72" s="46"/>
-      <c r="C72" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D72" s="233"/>
-      <c r="E72" s="233"/>
-      <c r="F72" s="233"/>
-      <c r="G72" s="234"/>
+      <c r="C72" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D72" s="273"/>
+      <c r="E72" s="273"/>
+      <c r="F72" s="273"/>
+      <c r="G72" s="274"/>
       <c r="H72" s="122"/>
       <c r="I72" s="220"/>
       <c r="J72" s="89"/>
@@ -8563,9 +8489,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD73" s="60">
-        <v>2</v>
-      </c>
+      <c r="AD73" s="60"/>
       <c r="AE73" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -8625,13 +8549,13 @@
     <row r="74" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A74" s="45"/>
       <c r="B74" s="46"/>
-      <c r="C74" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D74" s="233"/>
-      <c r="E74" s="233"/>
-      <c r="F74" s="233"/>
-      <c r="G74" s="234"/>
+      <c r="C74" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D74" s="273"/>
+      <c r="E74" s="273"/>
+      <c r="F74" s="273"/>
+      <c r="G74" s="274"/>
       <c r="H74" s="122"/>
       <c r="I74" s="220"/>
       <c r="J74" s="89"/>
@@ -8730,9 +8654,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD75" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD75" s="109"/>
       <c r="AE75" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -8792,13 +8714,13 @@
     <row r="76" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A76" s="45"/>
       <c r="B76" s="46"/>
-      <c r="C76" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D76" s="233"/>
-      <c r="E76" s="233"/>
-      <c r="F76" s="233"/>
-      <c r="G76" s="234"/>
+      <c r="C76" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D76" s="273"/>
+      <c r="E76" s="273"/>
+      <c r="F76" s="273"/>
+      <c r="G76" s="274"/>
       <c r="H76" s="122"/>
       <c r="I76" s="220"/>
       <c r="J76" s="89"/>
@@ -8897,9 +8819,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD77" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD77" s="109"/>
       <c r="AE77" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -8959,13 +8879,13 @@
     <row r="78" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A78" s="45"/>
       <c r="B78" s="46"/>
-      <c r="C78" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D78" s="233"/>
-      <c r="E78" s="233"/>
-      <c r="F78" s="233"/>
-      <c r="G78" s="234"/>
+      <c r="C78" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D78" s="273"/>
+      <c r="E78" s="273"/>
+      <c r="F78" s="273"/>
+      <c r="G78" s="274"/>
       <c r="H78" s="122"/>
       <c r="I78" s="220"/>
       <c r="J78" s="89"/>
@@ -9064,9 +8984,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD79" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD79" s="109"/>
       <c r="AE79" s="56" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -9126,13 +9044,13 @@
     <row r="80" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A80" s="45"/>
       <c r="B80" s="46"/>
-      <c r="C80" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D80" s="233"/>
-      <c r="E80" s="233"/>
-      <c r="F80" s="233"/>
-      <c r="G80" s="234"/>
+      <c r="C80" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D80" s="273"/>
+      <c r="E80" s="273"/>
+      <c r="F80" s="273"/>
+      <c r="G80" s="274"/>
       <c r="H80" s="122"/>
       <c r="I80" s="220"/>
       <c r="J80" s="89"/>
@@ -9231,9 +9149,7 @@
         <f t="shared" ref="AC81:AC144" si="73">IF(AB81&gt;=13,13,AB81)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD81" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD81" s="109"/>
       <c r="AE81" s="56" t="e">
         <f t="shared" ref="AE81:AE144" si="74">IF((AC81+AD81)&gt;=15,15,(AC81+AD81))</f>
         <v>#DIV/0!</v>
@@ -9293,13 +9209,13 @@
     <row r="82" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A82" s="45"/>
       <c r="B82" s="46"/>
-      <c r="C82" s="232" t="s">
-        <v>67</v>
-      </c>
-      <c r="D82" s="233"/>
-      <c r="E82" s="233"/>
-      <c r="F82" s="233"/>
-      <c r="G82" s="234"/>
+      <c r="C82" s="272" t="s">
+        <v>66</v>
+      </c>
+      <c r="D82" s="273"/>
+      <c r="E82" s="273"/>
+      <c r="F82" s="273"/>
+      <c r="G82" s="274"/>
       <c r="H82" s="122"/>
       <c r="I82" s="220"/>
       <c r="J82" s="89"/>
@@ -9398,9 +9314,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD83" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD83" s="109"/>
       <c r="AE83" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -9460,13 +9374,13 @@
     <row r="84" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A84" s="45"/>
       <c r="B84" s="46"/>
-      <c r="C84" s="232" t="s">
-        <v>67</v>
-      </c>
-      <c r="D84" s="233"/>
-      <c r="E84" s="233"/>
-      <c r="F84" s="233"/>
-      <c r="G84" s="234"/>
+      <c r="C84" s="272" t="s">
+        <v>66</v>
+      </c>
+      <c r="D84" s="273"/>
+      <c r="E84" s="273"/>
+      <c r="F84" s="273"/>
+      <c r="G84" s="274"/>
       <c r="H84" s="122"/>
       <c r="I84" s="220"/>
       <c r="J84" s="89"/>
@@ -9565,9 +9479,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD85" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD85" s="109"/>
       <c r="AE85" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -9627,13 +9539,13 @@
     <row r="86" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A86" s="45"/>
       <c r="B86" s="46"/>
-      <c r="C86" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D86" s="233"/>
-      <c r="E86" s="233"/>
-      <c r="F86" s="233"/>
-      <c r="G86" s="234"/>
+      <c r="C86" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D86" s="273"/>
+      <c r="E86" s="273"/>
+      <c r="F86" s="273"/>
+      <c r="G86" s="274"/>
       <c r="H86" s="122"/>
       <c r="I86" s="220"/>
       <c r="J86" s="89"/>
@@ -9732,9 +9644,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD87" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD87" s="109"/>
       <c r="AE87" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -9794,13 +9704,13 @@
     <row r="88" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A88" s="45"/>
       <c r="B88" s="46"/>
-      <c r="C88" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="D88" s="233"/>
-      <c r="E88" s="233"/>
-      <c r="F88" s="233"/>
-      <c r="G88" s="234"/>
+      <c r="C88" s="272" t="s">
+        <v>63</v>
+      </c>
+      <c r="D88" s="273"/>
+      <c r="E88" s="273"/>
+      <c r="F88" s="273"/>
+      <c r="G88" s="274"/>
       <c r="H88" s="122"/>
       <c r="I88" s="220"/>
       <c r="J88" s="89"/>
@@ -9899,9 +9809,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD89" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD89" s="109"/>
       <c r="AE89" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -10005,9 +9913,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD90" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD90" s="109"/>
       <c r="AE90" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -10111,9 +10017,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD91" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD91" s="109"/>
       <c r="AE91" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -10217,9 +10121,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD92" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD92" s="109"/>
       <c r="AE92" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -10323,9 +10225,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD93" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD93" s="109"/>
       <c r="AE93" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -10429,9 +10329,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD94" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD94" s="109"/>
       <c r="AE94" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -10535,9 +10433,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD95" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD95" s="109"/>
       <c r="AE95" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -10641,9 +10537,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD96" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD96" s="109"/>
       <c r="AE96" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -10747,9 +10641,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD97" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD97" s="109"/>
       <c r="AE97" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -10853,9 +10745,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD98" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD98" s="109"/>
       <c r="AE98" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -10959,9 +10849,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD99" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD99" s="109"/>
       <c r="AE99" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -11065,9 +10953,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD100" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD100" s="109"/>
       <c r="AE100" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -11171,9 +11057,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD101" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD101" s="109"/>
       <c r="AE101" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -11277,9 +11161,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD102" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD102" s="109"/>
       <c r="AE102" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -11383,9 +11265,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD103" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD103" s="109"/>
       <c r="AE103" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -11489,9 +11369,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD104" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD104" s="109"/>
       <c r="AE104" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -11595,9 +11473,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD105" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD105" s="109"/>
       <c r="AE105" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -11701,9 +11577,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD106" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD106" s="109"/>
       <c r="AE106" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -11807,9 +11681,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD107" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD107" s="109"/>
       <c r="AE107" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -11913,9 +11785,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD108" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD108" s="109"/>
       <c r="AE108" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -12019,9 +11889,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD109" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD109" s="109"/>
       <c r="AE109" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -12125,9 +11993,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD110" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD110" s="109"/>
       <c r="AE110" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -12231,9 +12097,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD111" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD111" s="109"/>
       <c r="AE111" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -12337,9 +12201,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD112" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD112" s="109"/>
       <c r="AE112" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -12443,9 +12305,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD113" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD113" s="109"/>
       <c r="AE113" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -12549,9 +12409,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD114" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD114" s="109"/>
       <c r="AE114" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -12655,9 +12513,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD115" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD115" s="109"/>
       <c r="AE115" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -12761,9 +12617,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD116" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD116" s="109"/>
       <c r="AE116" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -12867,9 +12721,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD117" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD117" s="109"/>
       <c r="AE117" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -12973,9 +12825,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD118" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD118" s="109"/>
       <c r="AE118" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -13079,9 +12929,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD119" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD119" s="109"/>
       <c r="AE119" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -13185,9 +13033,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD120" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD120" s="109"/>
       <c r="AE120" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -13291,9 +13137,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD121" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD121" s="109"/>
       <c r="AE121" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -13397,9 +13241,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD122" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD122" s="109"/>
       <c r="AE122" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -13503,9 +13345,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD123" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD123" s="109"/>
       <c r="AE123" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -13609,9 +13449,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD124" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD124" s="109"/>
       <c r="AE124" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -13715,9 +13553,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD125" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD125" s="109"/>
       <c r="AE125" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -13821,9 +13657,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD126" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD126" s="109"/>
       <c r="AE126" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -13927,9 +13761,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD127" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD127" s="109"/>
       <c r="AE127" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -14033,9 +13865,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD128" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD128" s="109"/>
       <c r="AE128" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -14139,9 +13969,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD129" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD129" s="109"/>
       <c r="AE129" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -14245,9 +14073,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD130" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD130" s="109"/>
       <c r="AE130" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -14351,9 +14177,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD131" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD131" s="109"/>
       <c r="AE131" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -14457,9 +14281,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD132" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD132" s="109"/>
       <c r="AE132" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -14563,9 +14385,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD133" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD133" s="109"/>
       <c r="AE133" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -14669,9 +14489,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD134" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD134" s="109"/>
       <c r="AE134" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -14775,9 +14593,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD135" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD135" s="109"/>
       <c r="AE135" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -14881,9 +14697,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD136" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD136" s="109"/>
       <c r="AE136" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -14987,9 +14801,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD137" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD137" s="109"/>
       <c r="AE137" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -15093,9 +14905,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD138" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD138" s="109"/>
       <c r="AE138" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -15199,9 +15009,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD139" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD139" s="109"/>
       <c r="AE139" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -15305,9 +15113,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD140" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD140" s="109"/>
       <c r="AE140" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -15411,9 +15217,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD141" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD141" s="109"/>
       <c r="AE141" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -15517,9 +15321,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD142" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD142" s="109"/>
       <c r="AE142" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -15623,9 +15425,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD143" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD143" s="109"/>
       <c r="AE143" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -15729,9 +15529,7 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD144" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD144" s="109"/>
       <c r="AE144" s="56" t="e">
         <f t="shared" si="74"/>
         <v>#DIV/0!</v>
@@ -15835,9 +15633,7 @@
         <f>IF(AB145&gt;=13,13,AB145)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD145" s="109">
-        <v>2</v>
-      </c>
+      <c r="AD145" s="109"/>
       <c r="AE145" s="56" t="e">
         <f>IF((AC145+AD145)&gt;=15,15,(AC145+AD145))</f>
         <v>#DIV/0!</v>
@@ -15896,33 +15692,42 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="AG1:AJ1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AD2:AL2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AQ3:AQ4"/>
-    <mergeCell ref="AR3:AR4"/>
-    <mergeCell ref="AS3:AS4"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:U3"/>
-    <mergeCell ref="W3:AE3"/>
-    <mergeCell ref="AF3:AM3"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C24:G24"/>
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="AZ3:AZ4"/>
     <mergeCell ref="C6:G6"/>
@@ -15939,42 +15744,33 @@
     <mergeCell ref="AN3:AN4"/>
     <mergeCell ref="AO3:AO4"/>
     <mergeCell ref="AP3:AP4"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="AQ3:AQ4"/>
+    <mergeCell ref="AR3:AR4"/>
+    <mergeCell ref="AS3:AS4"/>
+    <mergeCell ref="AU2:AV2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:U3"/>
+    <mergeCell ref="W3:AE3"/>
+    <mergeCell ref="AF3:AM3"/>
+    <mergeCell ref="AG1:AJ1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AD2:AL2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AE1:AF1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
